--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SALTILLO VILLALTA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SALTILLO VILLALTA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC36"/>
+  <dimension ref="A1:AC43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -864,12 +864,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>338269</t>
+          <t>347290</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16087</t>
+          <t>89455</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GIEZI</t>
+          <t xml:space="preserve">VELLADURAI </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>KIRUTHIKA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>KIRUTHIKA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -899,10 +899,14 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8441063703</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>8321234660</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>RANCHO DE PEÑA</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -910,17 +914,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>12-10-1978</t>
+          <t>02-03-1999</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>GIEZID@HOTMAIL.COM</t>
+          <t>V.KIRTHI2399@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>27-01-2026 08:06:24</t>
+          <t>01-03-2026 10:03:45</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -930,36 +934,44 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>3 MESES $2,099</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>699.67</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 17:17:39</t>
+          <t>01-03-2026 10:09:05</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>01-03-2026 10:08:26</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -967,36 +979,36 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26330522805800003157</t>
+          <t>26330522766350003039</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexander Osorio Padua</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347511</t>
+          <t>347304</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89676</t>
+          <t>89469</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1006,17 +1018,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>XIMENA</t>
+          <t>DANIEL</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HUMARAN</t>
+          <t>GARZA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CALDERON</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1026,32 +1038,32 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8715683348</t>
+          <t>8442345269</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">C DE LA CANTERA </t>
+          <t>FLORES TAPIA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>06-11-2004</t>
+          <t>20-07-1996</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>XIMENAHUMC@GMAIL.COM</t>
+          <t>DANY_GARZA96@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 11:42:38</t>
+          <t>01-03-2026 10:51:59</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1061,32 +1073,32 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 11:47:59</t>
+          <t>01-03-2026 11:00:49</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>02-03-2026 11:47:04</t>
+          <t>01-03-2026 10:59:52</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1096,7 +1108,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1106,14 +1118,18 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26330522789760003088</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
+          <t>26330522767210003045</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1130,12 +1146,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347290</t>
+          <t>347294</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89455</t>
+          <t>89459</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1145,17 +1161,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">VELLADURAI </t>
+          <t>KANNAN</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KIRUTHIKA</t>
+          <t>VINODHINI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>KIRUTHIKA</t>
+          <t>VINODHINI</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1165,12 +1181,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8321234660</t>
+          <t>8446636981</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>RANCHO DE PEÑA</t>
+          <t>FLORES CAÑDA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1180,17 +1196,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>02-03-1999</t>
+          <t>04-09-1996</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>V.KIRTHI2399@GMAIL.COM</t>
+          <t>VINODHINIKANNAN1996@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>01-03-2026 10:03:45</t>
+          <t>01-03-2026 10:14:17</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1215,7 +1231,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>01-03-2026 10:09:05</t>
+          <t>01-03-2026 10:17:22</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1225,7 +1241,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>01-03-2026 10:08:26</t>
+          <t>01-03-2026 10:16:36</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1245,7 +1261,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26330522766350003039</t>
+          <t>26330522766510003040</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1269,12 +1285,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347304</t>
+          <t>347295</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89469</t>
+          <t>89460</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1284,17 +1300,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DANIEL</t>
+          <t>BABU</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>GARZA</t>
+          <t>AJITH</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>KUMAR</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1304,12 +1320,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8442345269</t>
+          <t>8446636984</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>FLORES TAPIA</t>
+          <t xml:space="preserve">RANCHO DE PEÑA </t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1319,17 +1335,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>20-07-1996</t>
+          <t>23-04-1997</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>DANY_GARZA96@HOTMAIL.COM</t>
+          <t>B.AJITHSASI0223@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>01-03-2026 10:51:59</t>
+          <t>01-03-2026 10:21:27</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1354,7 +1370,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>01-03-2026 11:00:49</t>
+          <t>01-03-2026 10:25:28</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1364,7 +1380,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>01-03-2026 10:59:52</t>
+          <t>01-03-2026 10:24:48</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1374,7 +1390,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1384,14 +1400,10 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26330522767210003045</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26330522766600003042</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1400,24 +1412,24 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexander Osorio Padua</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347459</t>
+          <t>345411</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89624</t>
+          <t>87576</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1427,17 +1439,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">RICARDO </t>
+          <t xml:space="preserve">JOSE ARMANDO </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOLEDO </t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>PIZAÑA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1447,12 +1459,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8441225811</t>
+          <t>8661612658</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>RIO MISSISSIPI 215</t>
+          <t>COLONIA RANCHO DE PEÑA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1462,17 +1474,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>04-08-1985</t>
+          <t>19-09-2002</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>RTV_26720@HOTMAIL.COM</t>
+          <t>JOSEARMANDO190902@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 08:58:04</t>
+          <t>20-02-2026 19:45:12</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1482,32 +1494,32 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 09:12:03</t>
+          <t>03-03-2026 16:39:11</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>02-03-2026 09:10:56</t>
+          <t>03-03-2026 16:38:34</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1527,18 +1539,22 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26330522785400003078</t>
+          <t>26330522847440003233</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>SERGIO AARON CRUZ RODRIGUEZ</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1555,12 +1571,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347395</t>
+          <t>345884</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89560</t>
+          <t>88049</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1570,17 +1586,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">FERNANDA MITCHELL </t>
+          <t xml:space="preserve">JUAN CARLOS </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>OCHOA</t>
+          <t>CENTENO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>RIESTRA</t>
+          <t xml:space="preserve">MALDONADO </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1590,32 +1606,32 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8448587771</t>
+          <t>8116002358</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIA REAL </t>
+          <t>H11</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>18-01-2002</t>
+          <t>15-07-1970</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>FERNANDAMITCHEL8A@GMAIL.COM</t>
+          <t>CENTENOJUAN@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 05:57:55</t>
+          <t>23-02-2026 16:40:23</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1625,22 +1641,22 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 06:08:53</t>
+          <t>02-03-2026 09:15:34</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1650,7 +1666,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>02-03-2026 06:07:47</t>
+          <t>02-03-2026 09:14:39</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1670,36 +1686,44 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26330522774380003069</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
+          <t>26330522785540003080</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>SERGIO AARON CRUZ RODRIGUEZ</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Enrique Ramos Calvillo</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347294</t>
+          <t>338269</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89459</t>
+          <t>16087</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1709,17 +1733,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>KANNAN</t>
+          <t>GIEZI</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>VINODHINI</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>VINODHINI</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1729,14 +1753,10 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8446636981</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>FLORES CAÑDA</t>
-        </is>
-      </c>
+          <t>8441063703</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1744,17 +1764,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>04-09-1996</t>
+          <t>12-10-1978</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>VINODHINIKANNAN1996@GMAIL.COM</t>
+          <t>GIEZID@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>01-03-2026 10:14:17</t>
+          <t>27-01-2026 08:06:24</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1764,44 +1784,36 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>3 MESES $2,099</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>699.67</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>01-03-2026 10:17:22</t>
+          <t>02-03-2026 17:17:39</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>01-03-2026 10:16:36</t>
-        </is>
-      </c>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1809,36 +1821,36 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26330522766510003040</t>
+          <t>26330522805800003157</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Alexander Osorio Padua</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347295</t>
+          <t>347946</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>89460</t>
+          <t>90111</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1848,12 +1860,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>BABU</t>
+          <t>SEVANNA ARUNAGIRI</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AJITH</t>
+          <t>VINODH</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1868,12 +1880,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8446636984</t>
+          <t>8442891827</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">RANCHO DE PEÑA </t>
+          <t xml:space="preserve">CAÑADA ANCHA </t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1883,17 +1895,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>23-04-1997</t>
+          <t>02-12-1990</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>B.AJITHSASI0223@GMAIL.COM</t>
+          <t>VINODHARUNAGIRI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>01-03-2026 10:21:27</t>
+          <t>03-03-2026 07:18:02</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1918,17 +1930,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>01-03-2026 10:25:28</t>
+          <t>03-03-2026 07:50:25</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>01-03-2026 10:24:48</t>
+          <t>03-03-2026 07:49:38</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1938,7 +1950,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1948,10 +1960,14 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26330522766600003042</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr"/>
+          <t>26330522832300003202</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1960,12 +1976,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Alexander Osorio Padua</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -2258,12 +2274,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347172</t>
+          <t>347395</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>89337</t>
+          <t>89560</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2273,17 +2289,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DEYDA BERENICE</t>
+          <t xml:space="preserve">FERNANDA MITCHELL </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>VITELA</t>
+          <t>OCHOA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>RIESTRA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2293,12 +2309,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8448087408</t>
+          <t>8448587771</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>REAL DE PEÑA</t>
+          <t xml:space="preserve">VIA REAL </t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2308,17 +2324,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>27-11-1978</t>
+          <t>18-01-2002</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>DEBEVICO@HOTMAIL.COM</t>
+          <t>FERNANDAMITCHEL8A@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>28-02-2026 09:48:36</t>
+          <t>02-03-2026 05:57:55</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2328,32 +2344,32 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>02-03-2026 18:12:51</t>
+          <t>02-03-2026 06:08:53</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>02-03-2026 18:11:48</t>
+          <t>02-03-2026 06:07:47</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2363,7 +2379,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2373,22 +2389,14 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26330522810710003172</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>CHRISTIAN EDGARDO MARQUEZ DE LUNA</t>
-        </is>
-      </c>
+          <t>26330522774380003069</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2405,12 +2413,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347276</t>
+          <t>347732</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>89441</t>
+          <t>89897</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2420,17 +2428,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">SI </t>
+          <t>LUIS ANTONIO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PING</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ZENG</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2440,7 +2448,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5577351941</t>
+          <t>8443407772</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2451,17 +2459,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>26-02-1992</t>
+          <t>07-05-2011</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>MARCOS120734@GMAIL.COM</t>
+          <t>GIEZI12@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>01-03-2026 08:47:50</t>
+          <t>02-03-2026 17:19:27</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2486,12 +2494,12 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>01-03-2026 08:50:14</t>
+          <t>02-03-2026 17:21:11</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>02-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -2508,7 +2516,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26330522765180003033</t>
+          <t>26330522806080003158</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
@@ -2532,12 +2540,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>345884</t>
+          <t>347459</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>88049</t>
+          <t>89624</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2547,17 +2555,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN CARLOS </t>
+          <t xml:space="preserve">RICARDO </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CENTENO</t>
+          <t xml:space="preserve">TOLEDO </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">MALDONADO </t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2567,12 +2575,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8116002358</t>
+          <t>8441225811</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>H11</t>
+          <t>RIO MISSISSIPI 215</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2582,17 +2590,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>15-07-1970</t>
+          <t>04-08-1985</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CENTENOJUAN@HOTMAIL.COM</t>
+          <t>RTV_26720@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>23-02-2026 16:40:23</t>
+          <t>02-03-2026 08:58:04</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2602,22 +2610,22 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>02-03-2026 09:15:34</t>
+          <t>02-03-2026 09:12:03</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2627,7 +2635,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>02-03-2026 09:14:39</t>
+          <t>02-03-2026 09:10:56</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2637,7 +2645,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2647,22 +2655,18 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26330522785540003080</t>
+          <t>26330522785400003078</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>SERGIO AARON CRUZ RODRIGUEZ</t>
-        </is>
-      </c>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2679,12 +2683,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>347287</t>
+          <t>347615</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>89452</t>
+          <t>89780</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2694,17 +2698,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">KONDURAM </t>
+          <t>ZAHIRA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SANKARPANDI</t>
+          <t>GARZA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SANKARPANDI</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2714,32 +2718,32 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8446638777</t>
+          <t>8442917170</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>RANCHO DE PEÑA</t>
+          <t xml:space="preserve">ZOBA CENTRO </t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>28-07-1993</t>
+          <t>16-12-1992</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>SANKARPANDI589@GMAIL.COM</t>
+          <t>DANIELA162416@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>01-03-2026 09:50:34</t>
+          <t>02-03-2026 15:04:37</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2764,17 +2768,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>01-03-2026 10:00:47</t>
+          <t>02-03-2026 15:17:40</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>01-03-2026 09:59:47</t>
+          <t>02-03-2026 15:07:09</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2794,7 +2798,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26330522766130003038</t>
+          <t>26330522797160003110</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
@@ -2806,24 +2810,24 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Alexander Osorio Padua</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>347470</t>
+          <t>347665</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>89635</t>
+          <t>89830</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2833,17 +2837,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ABEL FRANCISCO</t>
+          <t>KARINA MONTSERRAT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FIGUEROA</t>
+          <t>MEDELLIN</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MONSIVAIS</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2853,32 +2857,32 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8442771751</t>
+          <t>8443422445</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>PLAZA DE MORELIA 148</t>
+          <t>EUROPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>28-11-1997</t>
+          <t>10-07-2003</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>ABEL_SW94@HOTMAIL.COM</t>
+          <t>MMEDELLIN.1089@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>02-03-2026 09:49:13</t>
+          <t>02-03-2026 16:10:21</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2903,7 +2907,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>02-03-2026 09:56:44</t>
+          <t>02-03-2026 16:14:32</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2913,7 +2917,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>02-03-2026 09:56:01</t>
+          <t>02-03-2026 16:14:00</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2933,7 +2937,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26330522786770003083</t>
+          <t>26330522800610003133</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
@@ -2957,12 +2961,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>347732</t>
+          <t>347714</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>89897</t>
+          <t>89879</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2972,17 +2976,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LUIS ANTONIO</t>
+          <t xml:space="preserve">MARTHA ALICIA </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t xml:space="preserve">RIVERA </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t xml:space="preserve">SAUCEDO </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2992,28 +2996,32 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8443407772</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>8442646668</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>PORTAL</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>07-05-2011</t>
+          <t>03-08-1958</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>GIEZI12@GMAIL.COM</t>
+          <t>RIVALICIA111@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>02-03-2026 17:19:27</t>
+          <t>02-03-2026 16:59:22</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3023,36 +3031,44 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>3 MESES $2,099</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>699.67</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>02-03-2026 17:21:11</t>
+          <t>03-03-2026 16:53:07</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:52:11</t>
+        </is>
+      </c>
       <c r="U19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W19" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3060,14 +3076,18 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26330522806080003158</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr"/>
+          <t>26330522848380003240</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -3084,12 +3104,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>347615</t>
+          <t>347664</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>89780</t>
+          <t>89829</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3099,17 +3119,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ZAHIRA</t>
+          <t xml:space="preserve">JAZMIN ESMERALDA </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>GARZA</t>
+          <t xml:space="preserve">SANDOVAL </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3119,12 +3139,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8442917170</t>
+          <t>8445411918</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZOBA CENTRO </t>
+          <t>RAMOS ARIZAPE</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3134,17 +3154,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>16-12-1992</t>
+          <t>04-09-2002</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>DANIELA162416@GMAIL.COM</t>
+          <t>ESMERALDASANDOVAL0409@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>02-03-2026 15:04:37</t>
+          <t>02-03-2026 16:09:58</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3169,7 +3189,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>02-03-2026 15:17:40</t>
+          <t>02-03-2026 16:13:39</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -3179,7 +3199,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>02-03-2026 15:07:09</t>
+          <t>02-03-2026 16:13:01</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3199,7 +3219,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26330522797160003110</t>
+          <t>26330522800540003132</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
@@ -3223,12 +3243,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>347665</t>
+          <t>347700</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>89830</t>
+          <t>89865</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3238,17 +3258,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>KARINA MONTSERRAT</t>
+          <t>MARTHA CHARLOTE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MEDELLIN</t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t xml:space="preserve">MULLER </t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3258,12 +3278,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>8443422445</t>
+          <t>8444274800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>EUROPA</t>
+          <t xml:space="preserve">PLAYA EL PALMAR </t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3273,17 +3293,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>10-07-2003</t>
+          <t>16-06-1984</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>MMEDELLIN.1089@GMAIL.COM</t>
+          <t>CHARLOTTEPVEM@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>02-03-2026 16:10:21</t>
+          <t>02-03-2026 16:44:57</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3293,22 +3313,22 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>02-03-2026 16:14:32</t>
+          <t>02-03-2026 16:51:01</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -3318,7 +3338,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>02-03-2026 16:14:00</t>
+          <t>02-03-2026 16:49:45</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3328,7 +3348,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3338,14 +3358,14 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26330522800610003133</t>
+          <t>26330522803450003142</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -3362,12 +3382,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>347638</t>
+          <t>347287</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>89803</t>
+          <t>89452</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3377,17 +3397,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">OMAR </t>
+          <t xml:space="preserve">KONDURAM </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t>SANKARPANDI</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUGO </t>
+          <t>SANKARPANDI</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3397,12 +3417,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>8441025582</t>
+          <t>8446638777</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>VILLA SANTA ELENA 185</t>
+          <t>RANCHO DE PEÑA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3412,17 +3432,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>15-12-1969</t>
+          <t>28-07-1993</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>DMTYGALO@GMAIL.COM</t>
+          <t>SANKARPANDI589@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>02-03-2026 15:37:11</t>
+          <t>01-03-2026 09:50:34</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3447,17 +3467,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>02-03-2026 15:43:24</t>
+          <t>01-03-2026 10:00:47</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>02-03-2026 15:42:29</t>
+          <t>01-03-2026 09:59:47</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3467,7 +3487,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3477,7 +3497,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26330522798470003120</t>
+          <t>26330522766130003038</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
@@ -3489,24 +3509,24 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexander Osorio Padua</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>347693</t>
+          <t>347470</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>89858</t>
+          <t>89635</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3516,17 +3536,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DANNA PATRICIA</t>
+          <t>ABEL FRANCISCO</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORENO </t>
+          <t>FIGUEROA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>PESINA</t>
+          <t>MONSIVAIS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3536,32 +3556,32 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>8444481303</t>
+          <t>8442771751</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>VILLAS DE RANCHO</t>
+          <t>PLAZA DE MORELIA 148</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>11-05-1979</t>
+          <t>28-11-1997</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>DANNA.MORENO@YAHOO.COM.MX</t>
+          <t>ABEL_SW94@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>02-03-2026 16:41:23</t>
+          <t>02-03-2026 09:49:13</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3586,7 +3606,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>02-03-2026 16:45:59</t>
+          <t>02-03-2026 09:56:44</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3596,7 +3616,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>02-03-2026 16:45:24</t>
+          <t>02-03-2026 09:56:01</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3606,7 +3626,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3616,7 +3636,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26330522802950003141</t>
+          <t>26330522786770003083</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
@@ -3640,12 +3660,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>347728</t>
+          <t>347476</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>89893</t>
+          <t>89641</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3655,17 +3675,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">PABLO  </t>
+          <t xml:space="preserve">LUIS RODRIGO </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">VELAZQUEZ </t>
+          <t>VALLE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLORES </t>
+          <t>SALAS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3675,12 +3695,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>8441104535</t>
+          <t>8441607089</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZONA CENTRO </t>
+          <t>C IRAN 639</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3690,17 +3710,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>16-01-2001</t>
+          <t>16-11-1992</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>PABLOCHARLESSV@GMAIL.COM</t>
+          <t>LUISRODRIGOVALLE@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>02-03-2026 17:16:48</t>
+          <t>02-03-2026 09:58:47</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3725,7 +3745,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>02-03-2026 17:25:15</t>
+          <t>02-03-2026 10:03:47</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3735,7 +3755,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>02-03-2026 17:22:49</t>
+          <t>02-03-2026 10:02:56</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3745,7 +3765,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3755,7 +3775,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26330522806360003159</t>
+          <t>26330522787040003084</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
@@ -3779,12 +3799,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>347743</t>
+          <t>347500</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>89908</t>
+          <t>89665</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3794,17 +3814,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAULA MARIA </t>
+          <t>GUSTAVO</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESQUIVEL </t>
+          <t>GUERRERO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>DAVILA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3814,32 +3834,32 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>8444642288</t>
+          <t>8441967822</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>VILLA VERGEL</t>
+          <t>LONGIN 244</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>05-09-2009</t>
+          <t>21-04-1994</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>PAO.ESQUIVEL0509@GMAIL.COM</t>
+          <t>GUSTAVOGUERREROHDZ21@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>02-03-2026 17:29:51</t>
+          <t>02-03-2026 11:04:17</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3849,22 +3869,22 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>02-03-2026 17:49:36</t>
+          <t>02-03-2026 11:09:31</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3874,7 +3894,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>02-03-2026 17:47:45</t>
+          <t>02-03-2026 11:08:44</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3884,7 +3904,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3894,18 +3914,14 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26330522808470003167</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26330522788690003086</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -3922,12 +3938,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>347664</t>
+          <t>347524</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>89829</t>
+          <t>89689</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3937,17 +3953,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">JAZMIN ESMERALDA </t>
+          <t>VICTOR MANUEL</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANDOVAL </t>
+          <t xml:space="preserve">SANTOS </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3957,32 +3973,32 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>8445411918</t>
+          <t>8771085725</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>RAMOS ARIZAPE</t>
+          <t xml:space="preserve">C MARMOL </t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>04-09-2002</t>
+          <t>13-11-1958</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>ESMERALDASANDOVAL0409@GMAIL.COM</t>
+          <t>VICMANSAN1@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>02-03-2026 16:09:58</t>
+          <t>02-03-2026 12:04:48</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3992,22 +4008,22 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>02-03-2026 16:13:39</t>
+          <t>02-03-2026 12:13:12</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -4017,7 +4033,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>02-03-2026 16:13:01</t>
+          <t>02-03-2026 12:12:09</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -4037,14 +4053,14 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26330522800540003132</t>
+          <t>26330522790550003092</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -4061,12 +4077,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>347700</t>
+          <t>347560</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>89865</t>
+          <t>89725</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4076,17 +4092,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MARTHA CHARLOTE</t>
+          <t>JOANA MELISSA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t xml:space="preserve">PEÑA </t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">MULLER </t>
+          <t xml:space="preserve">TORRES </t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4096,12 +4112,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>8444274800</t>
+          <t>8446072138</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLAYA EL PALMAR </t>
+          <t>JESUS CABELLO</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4111,17 +4127,17 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>16-06-1984</t>
+          <t>22-01-2001</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CHARLOTTEPVEM@GMAIL.COM</t>
+          <t>MELISS12_@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>02-03-2026 16:44:57</t>
+          <t>02-03-2026 13:15:33</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -4146,7 +4162,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>02-03-2026 16:51:01</t>
+          <t>02-03-2026 13:20:22</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -4156,7 +4172,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>02-03-2026 16:49:45</t>
+          <t>02-03-2026 13:19:38</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4176,7 +4192,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26330522803450003142</t>
+          <t>26330522792850003094</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
@@ -4200,12 +4216,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>347703</t>
+          <t>347659</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>89868</t>
+          <t>89824</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4215,17 +4231,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA JULIA </t>
+          <t xml:space="preserve">HANNA DANIELA </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t xml:space="preserve">RAMIREZ </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t xml:space="preserve">CARMONA </t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4235,12 +4251,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>8444972157</t>
+          <t>8443880461</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>PLAYA PALMAR</t>
+          <t>NISPERO 300</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4250,17 +4266,17 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>13-01-2002</t>
+          <t>22-12-2003</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>MARIAJULIARODGON12@GMAIL.COM</t>
+          <t>HANNARMZ2003@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>02-03-2026 16:46:35</t>
+          <t>02-03-2026 16:04:35</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4270,22 +4286,22 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>02-03-2026 16:56:06</t>
+          <t>02-03-2026 16:07:03</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -4295,7 +4311,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>02-03-2026 16:55:49</t>
+          <t>02-03-2026 16:06:28</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4305,7 +4321,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -4315,14 +4331,14 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26330522803920003147</t>
+          <t>26330522800060003129</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -4339,12 +4355,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>347741</t>
+          <t>347511</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>89906</t>
+          <t>89676</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4354,17 +4370,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALERIA </t>
+          <t>XIMENA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMIREZ </t>
+          <t>HUMARAN</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>CALDERON</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4374,10 +4390,14 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>8444556056</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>8715683348</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C DE LA CANTERA </t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4385,17 +4405,17 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>05-04-2013</t>
+          <t>06-11-2004</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>LUIS.RAMIREZ@VOSS.NET</t>
+          <t>XIMENAHUMC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>02-03-2026 17:24:53</t>
+          <t>02-03-2026 11:42:38</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4405,36 +4425,44 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>3 MESES $2,099</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>699.67</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>02-03-2026 17:26:15</t>
+          <t>02-03-2026 11:47:59</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>02-03-2026 11:47:04</t>
+        </is>
+      </c>
       <c r="U29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr"/>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4442,14 +4470,14 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26330522806500003160</t>
+          <t>26330522789760003088</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -4466,12 +4494,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>347476</t>
+          <t>347638</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>89641</t>
+          <t>89803</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4481,17 +4509,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS RODRIGO </t>
+          <t xml:space="preserve">OMAR </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>VALLE</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SALAS</t>
+          <t xml:space="preserve">LUGO </t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4501,12 +4529,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>8441607089</t>
+          <t>8441025582</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>C IRAN 639</t>
+          <t>VILLA SANTA ELENA 185</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4516,17 +4544,17 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>16-11-1992</t>
+          <t>15-12-1969</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>LUISRODRIGOVALLE@HOTMAIL.COM</t>
+          <t>DMTYGALO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>02-03-2026 09:58:47</t>
+          <t>02-03-2026 15:37:11</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4536,22 +4564,22 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>02-03-2026 10:03:47</t>
+          <t>02-03-2026 15:43:24</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -4561,7 +4589,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>02-03-2026 10:02:56</t>
+          <t>02-03-2026 15:42:29</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4581,14 +4609,14 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26330522787040003084</t>
+          <t>26330522798470003120</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -4605,12 +4633,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>347500</t>
+          <t>347693</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>89665</t>
+          <t>89858</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4620,17 +4648,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>GUSTAVO</t>
+          <t>DANNA PATRICIA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t xml:space="preserve">MORENO </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>PESINA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4640,32 +4668,32 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8441967822</t>
+          <t>8444481303</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>LONGIN 244</t>
+          <t>VILLAS DE RANCHO</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>21-04-1994</t>
+          <t>11-05-1979</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>GUSTAVOGUERREROHDZ21@GMAIL.COM</t>
+          <t>DANNA.MORENO@YAHOO.COM.MX</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>02-03-2026 11:04:17</t>
+          <t>02-03-2026 16:41:23</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4675,22 +4703,22 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>02-03-2026 11:09:31</t>
+          <t>02-03-2026 16:45:59</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4700,7 +4728,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>02-03-2026 11:08:44</t>
+          <t>02-03-2026 16:45:24</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4720,14 +4748,14 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26330522788690003086</t>
+          <t>26330522802950003141</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -4744,12 +4772,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>347524</t>
+          <t>347728</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>89689</t>
+          <t>89893</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4759,17 +4787,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VICTOR MANUEL</t>
+          <t xml:space="preserve">PABLO  </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTOS </t>
+          <t xml:space="preserve">VELAZQUEZ </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t xml:space="preserve">FLORES </t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4779,12 +4807,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>8771085725</t>
+          <t>8441104535</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">C MARMOL </t>
+          <t xml:space="preserve">ZONA CENTRO </t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4794,17 +4822,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>13-11-1958</t>
+          <t>16-01-2001</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>VICMANSAN1@HOTMAIL.COM</t>
+          <t>PABLOCHARLESSV@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>02-03-2026 12:04:48</t>
+          <t>02-03-2026 17:16:48</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4819,17 +4847,17 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>02-03-2026 12:13:12</t>
+          <t>02-03-2026 17:25:15</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4839,7 +4867,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>02-03-2026 12:12:09</t>
+          <t>02-03-2026 17:22:49</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4859,14 +4887,14 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26330522790550003092</t>
+          <t>26330522806360003159</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -4883,12 +4911,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>347560</t>
+          <t>347743</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>89725</t>
+          <t>89908</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4898,17 +4926,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>JOANA MELISSA</t>
+          <t xml:space="preserve">PAULA MARIA </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEÑA </t>
+          <t xml:space="preserve">ESQUIVEL </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">TORRES </t>
+          <t>DAVILA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4918,12 +4946,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>8446072138</t>
+          <t>8444642288</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>JESUS CABELLO</t>
+          <t>VILLA VERGEL</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4933,17 +4961,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>22-01-2001</t>
+          <t>05-09-2009</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>MELISS12_@HOTMAIL.COM</t>
+          <t>PAO.ESQUIVEL0509@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>02-03-2026 13:15:33</t>
+          <t>02-03-2026 17:29:51</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4953,22 +4981,22 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>02-03-2026 13:20:22</t>
+          <t>02-03-2026 17:49:36</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4978,7 +5006,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>02-03-2026 13:19:38</t>
+          <t>02-03-2026 17:47:45</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4988,7 +5016,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4998,14 +5026,18 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26330522792850003094</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr"/>
+          <t>26330522808470003167</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -5022,12 +5054,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>347659</t>
+          <t>348045</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>89824</t>
+          <t>90210</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5037,17 +5069,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">HANNA DANIELA </t>
+          <t xml:space="preserve">EDGAR ALEJANDRO </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMIREZ </t>
+          <t xml:space="preserve">CARLOS </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARMONA </t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -5057,32 +5089,32 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>8443880461</t>
+          <t>8444420576</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>NISPERO 300</t>
+          <t>LOC HEDIONDA GRANDE</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>22-12-2003</t>
+          <t>25-06-1986</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>HANNARMZ2003@GMAIL.COM</t>
+          <t>EDGAR.CARLOS@LIVE.COM.MX</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>02-03-2026 16:04:35</t>
+          <t>03-03-2026 13:30:38</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -5092,32 +5124,32 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>02-03-2026 16:07:03</t>
+          <t>03-03-2026 13:39:46</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>02-03-2026 16:06:28</t>
+          <t>03-03-2026 13:37:22</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -5137,14 +5169,14 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26330522800060003129</t>
+          <t>26330522840330003215</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -5161,12 +5193,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>347466</t>
+          <t>347172</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>89631</t>
+          <t>89337</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5176,17 +5208,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MARTIN ALEJANDRO</t>
+          <t>DEYDA BERENICE</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>VITELA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Y GAMEZ</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5196,32 +5228,32 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>8442734289</t>
+          <t>8448087408</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>PRIV BRUCELAS</t>
+          <t>REAL DE PEÑA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>07-09-2008</t>
+          <t>27-11-1978</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>MARINNNALEJANDRO@HOTMAIL.COM</t>
+          <t>DEBEVICO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>02-03-2026 09:35:39</t>
+          <t>28-02-2026 09:48:36</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5246,17 +5278,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>02-03-2026 09:41:18</t>
+          <t>02-03-2026 18:12:51</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>02-03-2026 09:39:57</t>
+          <t>02-03-2026 18:11:48</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5266,7 +5298,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -5276,11 +5308,19 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26330522786190003082</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
+          <t>26330522810710003172</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>CHRISTIAN EDGARDO MARQUEZ DE LUNA</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>649</t>
@@ -5300,12 +5340,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>347651</t>
+          <t>347276</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>89816</t>
+          <t>89441</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5315,17 +5355,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>GUILLERMO ROOSEVELTH</t>
+          <t xml:space="preserve">SI </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>NEIRA</t>
+          <t>PING</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>ZENG</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5335,14 +5375,10 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>8442180364</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>NORIA ARTEAGA 186</t>
-        </is>
-      </c>
+          <t>5577351941</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5350,17 +5386,17 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>15-07-1990</t>
+          <t>26-02-1992</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>ROOSEVELTH_SANTOS@HOTMAIL.COM</t>
+          <t>MARCOS120734@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>02-03-2026 15:51:57</t>
+          <t>01-03-2026 08:47:50</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -5370,44 +5406,36 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>3 MESES $2,099</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>699.67</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>02-03-2026 15:57:46</t>
+          <t>01-03-2026 08:50:14</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>02-03-2026 15:57:05</t>
-        </is>
-      </c>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5415,22 +5443,987 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26330522799370003124</t>
+          <t>26330522765180003033</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
+          <t>2099</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>347466</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>89631</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>MARTIN ALEJANDRO</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Y GAMEZ</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>8442734289</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>PRIV BRUCELAS</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>07-09-2008</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>MARINNNALEJANDRO@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>02-03-2026 09:35:39</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>02-03-2026 09:41:18</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>02-03-2026 09:39:57</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>26330522786190003082</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>347651</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>89816</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>GUILLERMO ROOSEVELTH</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>NEIRA</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>TORRES</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>8442180364</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>NORIA ARTEAGA 186</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>15-07-1990</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>ROOSEVELTH_SANTOS@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>02-03-2026 15:51:57</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>RECURRENTE $799 HE</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
           <t>799</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>02-03-2026 15:57:46</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>02-03-2026 15:57:05</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>26330522799370003124</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>347703</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>89868</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARIA JULIA </t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RODRIGUEZ </t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>8444972157</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>PLAYA PALMAR</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>13-01-2002</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>MARIAJULIARODGON12@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:46:35</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:56:06</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:55:49</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>26330522803920003147</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>347741</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>89906</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VALERIA </t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAMIREZ </t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>DIAZ</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>8444556056</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>05-04-2013</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>LUIS.RAMIREZ@VOSS.NET</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:24:53</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>3 MESES $2,099</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>699.67</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:26:15</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>26330522806500003160</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2099</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>347948</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>90113</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VELLATHUR </t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAMESH</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>GAYATHIRI</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>8445922584</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>CAÑADA ANCHA</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>20-05-1994</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>GAYATHIRIIVINODH@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>03-03-2026 07:22:19</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>03-03-2026 07:54:44</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>03-03-2026 07:53:56</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>26330522832440003203</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>348266</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>90431</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>CARRILLO</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>8446743787</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>GUAYULERA</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>25-04-2004</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>RODRIGUEZCARRILLOEDORDO7@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:25:46</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:30:40</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:29:57</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>26330522858970003271</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>348191</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>90356</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>JOSUE NERIM</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CASAS </t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>MOLINA</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>8443516231</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HACIENDA SAN RAFAEL </t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>18-02-1992</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>JOSUENERIM.1802@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:44:52</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:50:53</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:50:11</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>26330522852250003253</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SALTILLO VILLALTA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SALTILLO VILLALTA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC43"/>
+  <dimension ref="A1:AC66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>346355</t>
+          <t>347290</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>88520</t>
+          <t>89455</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EDGAR EMMANUEL</t>
+          <t xml:space="preserve">VELLADURAI </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>KIRUTHIKA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DE LEON</t>
+          <t>KIRUTHIKA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,32 +613,32 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8443430619</t>
+          <t>8321234660</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>VFVG</t>
+          <t>RANCHO DE PEÑA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>01-04-1983</t>
+          <t>02-03-1999</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>FASTVENDINGSALTILLO@GMAIL.COM</t>
+          <t>V.KIRTHI2399@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>25-02-2026 05:15:25</t>
+          <t>01-03-2026 10:03:45</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -663,17 +663,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 11:00:15</t>
+          <t>01-03-2026 10:09:05</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>02-03-2026 10:59:39</t>
+          <t>01-03-2026 10:08:26</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -693,19 +693,11 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26330522788500003085</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>CHRISTIAN EDGARDO MARQUEZ DE LUNA</t>
-        </is>
-      </c>
+          <t>26330522766350003039</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
           <t>649</t>
@@ -713,24 +705,24 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexander Osorio Padua</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>347312</t>
+          <t>347304</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>89477</t>
+          <t>89469</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -740,7 +732,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAGOBERTO </t>
+          <t>DANIEL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -760,12 +752,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8442440841</t>
+          <t>8442345269</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE MARIA MORELOS </t>
+          <t>FLORES TAPIA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -775,17 +767,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>26-02-1991</t>
+          <t>20-07-1996</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>DAGO_GARZA@HOTMAIL.COM</t>
+          <t>DANY_GARZA96@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>01-03-2026 11:02:16</t>
+          <t>01-03-2026 10:51:59</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -810,7 +802,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>01-03-2026 11:05:41</t>
+          <t>01-03-2026 11:00:49</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -820,7 +812,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>01-03-2026 11:04:52</t>
+          <t>01-03-2026 10:59:52</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -840,10 +832,14 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26330522767280003046</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr"/>
+          <t>26330522767210003045</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
@@ -864,12 +860,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347290</t>
+          <t>346927</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89455</t>
+          <t>89092</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -879,17 +875,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">VELLADURAI </t>
+          <t xml:space="preserve">ENRIQUE </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KIRUTHIKA</t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KIRUTHIKA</t>
+          <t>BLANCO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -899,32 +895,28 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8321234660</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>RANCHO DE PEÑA</t>
-        </is>
-      </c>
+          <t>8442183769</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>02-03-1999</t>
+          <t>31-08-1979</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>V.KIRTHI2399@GMAIL.COM</t>
+          <t>EGBEG@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>01-03-2026 10:03:45</t>
+          <t>27-02-2026 12:07:18</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -934,44 +926,36 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>ANUALIDAD + MES REGALO $6,999</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>538.38</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>01-03-2026 10:09:05</t>
+          <t>04-03-2026 04:56:24</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>01-03-2026 10:08:26</t>
-        </is>
-      </c>
+          <t>04-04-2027 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -979,36 +963,44 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26330522766350003039</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+          <t>26330522864020003284</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>CHRISTIAN EDGARDO MARQUEZ DE LUNA</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>6999</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Alexander Osorio Padua</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347304</t>
+          <t>340073</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89469</t>
+          <t>17891</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1018,17 +1010,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DANIEL</t>
+          <t>ANDREA ALEJANDRA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>GARZA</t>
+          <t>CONTRERAS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1038,32 +1030,32 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8442345269</t>
+          <t>8444958964</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FLORES TAPIA</t>
+          <t>HUERTO 225</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>20-07-1996</t>
+          <t>06-12-2002</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>DANY_GARZA96@HOTMAIL.COM</t>
+          <t>LUISANDREA.06@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>01-03-2026 10:51:59</t>
+          <t>02-02-2026 11:57:45</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1088,17 +1080,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>01-03-2026 11:00:49</t>
+          <t>02-03-2026 15:14:31</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>01-03-2026 10:59:52</t>
+          <t>02-03-2026 15:13:54</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1118,12 +1110,12 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26330522767210003045</t>
+          <t>26330522796990003109</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr"/>
@@ -1146,12 +1138,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347294</t>
+          <t>344818</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89459</t>
+          <t>22635</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1161,17 +1153,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>KANNAN</t>
+          <t>KEILA JUDITH</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>VINODHINI</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>VINODHINI</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1181,12 +1173,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8446636981</t>
+          <t>8441861104</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>FLORES CAÑDA</t>
+          <t>COLONIA REPUBLICA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1196,17 +1188,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>04-09-1996</t>
+          <t>18-12-1995</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>VINODHINIKANNAN1996@GMAIL.COM</t>
+          <t>KEILA.ABC@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>01-03-2026 10:14:17</t>
+          <t>18-02-2026 13:53:58</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1231,17 +1223,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>01-03-2026 10:17:22</t>
+          <t>02-03-2026 18:50:07</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>01-03-2026 10:16:36</t>
+          <t>02-03-2026 18:49:04</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1261,10 +1253,14 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26330522766510003040</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
+          <t>26330522814060003178</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1273,24 +1269,24 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Alexander Osorio Padua</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347295</t>
+          <t>338269</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89460</t>
+          <t>16087</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1300,17 +1296,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BABU</t>
+          <t>GIEZI</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AJITH</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>KUMAR</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1320,32 +1316,28 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8446636984</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RANCHO DE PEÑA </t>
-        </is>
-      </c>
+          <t>8441063703</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>23-04-1997</t>
+          <t>12-10-1978</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>B.AJITHSASI0223@GMAIL.COM</t>
+          <t>GIEZID@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>01-03-2026 10:21:27</t>
+          <t>27-01-2026 08:06:24</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1355,44 +1347,36 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>3 MESES $2,099</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>699.67</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>01-03-2026 10:25:28</t>
+          <t>02-03-2026 17:17:39</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>01-03-2026 10:24:48</t>
-        </is>
-      </c>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1400,36 +1384,36 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26330522766600003042</t>
+          <t>26330522805800003157</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Alexander Osorio Padua</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>345411</t>
+          <t>347459</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>87576</t>
+          <t>89624</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1439,17 +1423,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE ARMANDO </t>
+          <t xml:space="preserve">RICARDO </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t xml:space="preserve">TOLEDO </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PIZAÑA</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1459,12 +1443,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8661612658</t>
+          <t>8441225811</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>COLONIA RANCHO DE PEÑA</t>
+          <t>RIO MISSISSIPI 215</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1474,17 +1458,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>19-09-2002</t>
+          <t>04-08-1985</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>JOSEARMANDO190902@GMAIL.COM</t>
+          <t>RTV_26720@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>20-02-2026 19:45:12</t>
+          <t>02-03-2026 08:58:04</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1494,32 +1478,32 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>03-03-2026 16:39:11</t>
+          <t>02-03-2026 09:12:03</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>03-03-2026 16:38:34</t>
+          <t>02-03-2026 09:10:56</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1539,22 +1523,18 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26330522847440003233</t>
+          <t>26330522785400003078</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>SERGIO AARON CRUZ RODRIGUEZ</t>
-        </is>
-      </c>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1571,12 +1551,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>345884</t>
+          <t>347294</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>88049</t>
+          <t>89459</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1586,17 +1566,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN CARLOS </t>
+          <t>KANNAN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CENTENO</t>
+          <t>VINODHINI</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">MALDONADO </t>
+          <t>VINODHINI</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1606,32 +1586,32 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8116002358</t>
+          <t>8446636981</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>H11</t>
+          <t>FLORES CAÑDA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>15-07-1970</t>
+          <t>04-09-1996</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CENTENOJUAN@HOTMAIL.COM</t>
+          <t>VINODHINIKANNAN1996@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>23-02-2026 16:40:23</t>
+          <t>01-03-2026 10:14:17</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1656,17 +1636,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 09:15:34</t>
+          <t>01-03-2026 10:17:22</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>02-03-2026 09:14:39</t>
+          <t>01-03-2026 10:16:36</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1686,19 +1666,11 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26330522785540003080</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>SERGIO AARON CRUZ RODRIGUEZ</t>
-        </is>
-      </c>
+          <t>26330522766510003040</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
           <t>649</t>
@@ -1706,7 +1678,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Carlos Enrique Ramos Calvillo</t>
+          <t>Alexander Osorio Padua</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1718,12 +1690,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>338269</t>
+          <t>347295</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16087</t>
+          <t>89460</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1733,17 +1705,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>GIEZI</t>
+          <t>BABU</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>AJITH</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>KUMAR</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1753,28 +1725,32 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8441063703</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>8446636984</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RANCHO DE PEÑA </t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>12-10-1978</t>
+          <t>23-04-1997</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>GIEZID@HOTMAIL.COM</t>
+          <t>B.AJITHSASI0223@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>27-01-2026 08:06:24</t>
+          <t>01-03-2026 10:21:27</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1784,36 +1760,44 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>3 MESES $2,099</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>699.67</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-03-2026 17:17:39</t>
+          <t>01-03-2026 10:25:28</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>01-03-2026 10:24:48</t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1821,36 +1805,36 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26330522805800003157</t>
+          <t>26330522766600003042</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexander Osorio Padua</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347946</t>
+          <t>346355</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90111</t>
+          <t>88520</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1860,17 +1844,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SEVANNA ARUNAGIRI</t>
+          <t>EDGAR EMMANUEL</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>VINODH</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>KUMAR</t>
+          <t>DE LEON</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1880,12 +1864,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8442891827</t>
+          <t>8443430619</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAÑADA ANCHA </t>
+          <t>VFVG</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1895,17 +1879,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>02-12-1990</t>
+          <t>01-04-1983</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>VINODHARUNAGIRI@GMAIL.COM</t>
+          <t>FASTVENDINGSALTILLO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>03-03-2026 07:18:02</t>
+          <t>25-02-2026 05:15:25</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1930,17 +1914,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>03-03-2026 07:50:25</t>
+          <t>02-03-2026 11:00:15</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>03-03-2026 07:49:38</t>
+          <t>02-03-2026 10:59:39</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1960,15 +1944,19 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26330522832300003202</t>
+          <t>26330522788500003085</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>CHRISTIAN EDGARDO MARQUEZ DE LUNA</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>649</t>
@@ -1988,12 +1976,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>340073</t>
+          <t>347312</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>17891</t>
+          <t>89477</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2003,17 +1991,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ANDREA ALEJANDRA</t>
+          <t xml:space="preserve">DAGOBERTO </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CONTRERAS</t>
+          <t>GARZA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2023,32 +2011,32 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8444958964</t>
+          <t>8442440841</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>HUERTO 225</t>
+          <t xml:space="preserve">JOSE MARIA MORELOS </t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>06-12-2002</t>
+          <t>26-02-1991</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>LUISANDREA.06@OUTLOOK.COM</t>
+          <t>DAGO_GARZA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-02-2026 11:57:45</t>
+          <t>01-03-2026 11:02:16</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2073,17 +2061,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>02-03-2026 15:14:31</t>
+          <t>01-03-2026 11:05:41</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>02-03-2026 15:13:54</t>
+          <t>01-03-2026 11:04:52</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2103,14 +2091,10 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26330522796990003109</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26330522767280003046</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
@@ -2131,12 +2115,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>344818</t>
+          <t>345884</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>22635</t>
+          <t>88049</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2146,17 +2130,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>KEILA JUDITH</t>
+          <t xml:space="preserve">JUAN CARLOS </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>CENTENO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t xml:space="preserve">MALDONADO </t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2166,32 +2150,32 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8441861104</t>
+          <t>8116002358</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>COLONIA REPUBLICA</t>
+          <t>H11</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>18-12-1995</t>
+          <t>15-07-1970</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>KEILA.ABC@OUTLOOK.COM</t>
+          <t>CENTENOJUAN@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>18-02-2026 13:53:58</t>
+          <t>23-02-2026 16:40:23</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2216,7 +2200,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>02-03-2026 18:50:07</t>
+          <t>02-03-2026 09:15:34</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -2226,7 +2210,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>02-03-2026 18:49:04</t>
+          <t>02-03-2026 09:14:39</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2246,15 +2230,19 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26330522814060003178</t>
+          <t>26330522785540003080</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>SERGIO AARON CRUZ RODRIGUEZ</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>649</t>
@@ -2262,24 +2250,24 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Enrique Ramos Calvillo</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347395</t>
+          <t>347287</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>89560</t>
+          <t>89452</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2289,17 +2277,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">FERNANDA MITCHELL </t>
+          <t xml:space="preserve">KONDURAM </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>OCHOA</t>
+          <t>SANKARPANDI</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>RIESTRA</t>
+          <t>SANKARPANDI</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2309,32 +2297,32 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8448587771</t>
+          <t>8446638777</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIA REAL </t>
+          <t>RANCHO DE PEÑA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>18-01-2002</t>
+          <t>28-07-1993</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>FERNANDAMITCHEL8A@GMAIL.COM</t>
+          <t>SANKARPANDI589@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-03-2026 05:57:55</t>
+          <t>01-03-2026 09:50:34</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2344,32 +2332,32 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>02-03-2026 06:08:53</t>
+          <t>01-03-2026 10:00:47</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>02-03-2026 06:07:47</t>
+          <t>01-03-2026 09:59:47</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2389,36 +2377,36 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26330522774380003069</t>
+          <t>26330522766130003038</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexander Osorio Padua</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347732</t>
+          <t>347511</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>89897</t>
+          <t>89676</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2428,17 +2416,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LUIS ANTONIO</t>
+          <t>XIMENA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>HUMARAN</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>CALDERON</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2448,28 +2436,32 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8443407772</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>8715683348</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C DE LA CANTERA </t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>07-05-2011</t>
+          <t>06-11-2004</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>GIEZI12@GMAIL.COM</t>
+          <t>XIMENAHUMC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-03-2026 17:19:27</t>
+          <t>02-03-2026 11:42:38</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2479,36 +2471,44 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>3 MESES $2,099</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>699.67</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>02-03-2026 17:21:11</t>
+          <t>02-03-2026 11:47:59</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>02-03-2026 11:47:04</t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2516,14 +2516,14 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26330522806080003158</t>
+          <t>26330522789760003088</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2540,12 +2540,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>347459</t>
+          <t>347172</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>89624</t>
+          <t>89337</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2555,17 +2555,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">RICARDO </t>
+          <t>DEYDA BERENICE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOLEDO </t>
+          <t>VITELA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2575,32 +2575,32 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8441225811</t>
+          <t>8448087408</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>RIO MISSISSIPI 215</t>
+          <t>REAL DE PEÑA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>04-08-1985</t>
+          <t>27-11-1978</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>RTV_26720@HOTMAIL.COM</t>
+          <t>DEBEVICO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>02-03-2026 08:58:04</t>
+          <t>28-02-2026 09:48:36</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2610,32 +2610,32 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>02-03-2026 09:12:03</t>
+          <t>02-03-2026 18:12:51</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>02-03-2026 09:10:56</t>
+          <t>02-03-2026 18:11:48</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2655,18 +2655,22 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26330522785400003078</t>
+          <t>26330522810710003172</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>CHRISTIAN EDGARDO MARQUEZ DE LUNA</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2683,12 +2687,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>347615</t>
+          <t>347276</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>89780</t>
+          <t>89441</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2698,17 +2702,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ZAHIRA</t>
+          <t xml:space="preserve">SI </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>GARZA</t>
+          <t>PING</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>ZENG</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2718,32 +2722,28 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8442917170</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ZOBA CENTRO </t>
-        </is>
-      </c>
+          <t>5577351941</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>16-12-1992</t>
+          <t>26-02-1992</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>DANIELA162416@GMAIL.COM</t>
+          <t>MARCOS120734@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>02-03-2026 15:04:37</t>
+          <t>01-03-2026 08:47:50</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2753,44 +2753,36 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>3 MESES $2,099</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>699.67</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>02-03-2026 15:17:40</t>
+          <t>01-03-2026 08:50:14</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>02-03-2026 15:07:09</t>
-        </is>
-      </c>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2798,14 +2790,14 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26330522797160003110</t>
+          <t>26330522765180003033</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2822,12 +2814,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>347665</t>
+          <t>347410</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>89830</t>
+          <t>89575</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2837,17 +2829,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>KARINA MONTSERRAT</t>
+          <t>ANDRES</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MEDELLIN</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>ARENAS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2857,32 +2849,32 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8443422445</t>
+          <t>8444519851</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>EUROPA</t>
+          <t xml:space="preserve">NUEVO ATARDECER </t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>10-07-2003</t>
+          <t>02-05-2004</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>MMEDELLIN.1089@GMAIL.COM</t>
+          <t>AR0884520@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>02-03-2026 16:10:21</t>
+          <t>02-03-2026 06:56:57</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2892,32 +2884,32 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>02-03-2026 16:14:32</t>
+          <t>04-03-2026 16:26:40</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>02-03-2026 16:14:00</t>
+          <t>04-03-2026 16:24:22</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2927,7 +2919,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2937,14 +2929,14 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26330522800610003133</t>
+          <t>26330522887260003329</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2961,12 +2953,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>347714</t>
+          <t>347466</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>89879</t>
+          <t>89631</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2976,17 +2968,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTHA ALICIA </t>
+          <t>MARTIN ALEJANDRO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">RIVERA </t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAUCEDO </t>
+          <t>Y GAMEZ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2996,32 +2988,32 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8442646668</t>
+          <t>8442734289</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>PORTAL</t>
+          <t>PRIV BRUCELAS</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>03-08-1958</t>
+          <t>07-09-2008</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>RIVALICIA111@GMAIL.COM</t>
+          <t>MARINNNALEJANDRO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>02-03-2026 16:59:22</t>
+          <t>02-03-2026 09:35:39</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3031,32 +3023,32 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>03-03-2026 16:53:07</t>
+          <t>02-03-2026 09:41:18</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>03-03-2026 16:52:11</t>
+          <t>02-03-2026 09:39:57</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3076,18 +3068,14 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26330522848380003240</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26330522786190003082</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -3104,12 +3092,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>347664</t>
+          <t>347615</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>89829</t>
+          <t>89780</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3119,17 +3107,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">JAZMIN ESMERALDA </t>
+          <t>ZAHIRA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANDOVAL </t>
+          <t>GARZA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3139,12 +3127,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8445411918</t>
+          <t>8442917170</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>RAMOS ARIZAPE</t>
+          <t xml:space="preserve">ZOBA CENTRO </t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3154,17 +3142,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>04-09-2002</t>
+          <t>16-12-1992</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>ESMERALDASANDOVAL0409@GMAIL.COM</t>
+          <t>DANIELA162416@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>02-03-2026 16:09:58</t>
+          <t>02-03-2026 15:04:37</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3189,7 +3177,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>02-03-2026 16:13:39</t>
+          <t>02-03-2026 15:17:40</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -3199,7 +3187,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>02-03-2026 16:13:01</t>
+          <t>02-03-2026 15:07:09</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3219,7 +3207,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26330522800540003132</t>
+          <t>26330522797160003110</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
@@ -3243,12 +3231,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>347700</t>
+          <t>347665</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>89865</t>
+          <t>89830</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3258,17 +3246,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MARTHA CHARLOTE</t>
+          <t>KARINA MONTSERRAT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t>MEDELLIN</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">MULLER </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3278,12 +3266,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>8444274800</t>
+          <t>8443422445</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLAYA EL PALMAR </t>
+          <t>EUROPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3293,17 +3281,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>16-06-1984</t>
+          <t>10-07-2003</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CHARLOTTEPVEM@GMAIL.COM</t>
+          <t>MMEDELLIN.1089@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>02-03-2026 16:44:57</t>
+          <t>02-03-2026 16:10:21</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3313,22 +3301,22 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>02-03-2026 16:51:01</t>
+          <t>02-03-2026 16:14:32</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -3338,7 +3326,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>02-03-2026 16:49:45</t>
+          <t>02-03-2026 16:14:00</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3348,7 +3336,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3358,36 +3346,36 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26330522803450003142</t>
+          <t>26330522800610003133</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Gerardo Emmanuel Ramirez Sanchez</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>347287</t>
+          <t>347714</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>89452</t>
+          <t>89879</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3397,17 +3385,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">KONDURAM </t>
+          <t xml:space="preserve">MARTHA ALICIA </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SANKARPANDI</t>
+          <t xml:space="preserve">RIVERA </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SANKARPANDI</t>
+          <t xml:space="preserve">SAUCEDO </t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3417,32 +3405,32 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>8446638777</t>
+          <t>8442646668</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>RANCHO DE PEÑA</t>
+          <t>PORTAL</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>28-07-1993</t>
+          <t>03-08-1958</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>SANKARPANDI589@GMAIL.COM</t>
+          <t>RIVALICIA111@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>01-03-2026 09:50:34</t>
+          <t>02-03-2026 16:59:22</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3452,32 +3440,32 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>01-03-2026 10:00:47</t>
+          <t>03-03-2026 16:53:07</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>01-03-2026 09:59:47</t>
+          <t>03-03-2026 16:52:11</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3497,36 +3485,40 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26330522766130003038</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr"/>
+          <t>26330522848380003240</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Alexander Osorio Padua</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>347470</t>
+          <t>347664</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>89635</t>
+          <t>89829</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3536,17 +3528,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ABEL FRANCISCO</t>
+          <t xml:space="preserve">JAZMIN ESMERALDA </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FIGUEROA</t>
+          <t xml:space="preserve">SANDOVAL </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MONSIVAIS</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3556,32 +3548,32 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>8442771751</t>
+          <t>8445411918</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>PLAZA DE MORELIA 148</t>
+          <t>RAMOS ARIZAPE</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>28-11-1997</t>
+          <t>04-09-2002</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>ABEL_SW94@HOTMAIL.COM</t>
+          <t>ESMERALDASANDOVAL0409@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>02-03-2026 09:49:13</t>
+          <t>02-03-2026 16:09:58</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3591,22 +3583,22 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>02-03-2026 09:56:44</t>
+          <t>02-03-2026 16:13:39</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3616,7 +3608,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>02-03-2026 09:56:01</t>
+          <t>02-03-2026 16:13:01</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3626,7 +3618,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3636,36 +3628,36 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26330522786770003083</t>
+          <t>26330522800540003132</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Gerardo Emmanuel Ramirez Sanchez</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>347476</t>
+          <t>347700</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>89641</t>
+          <t>89865</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3675,17 +3667,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS RODRIGO </t>
+          <t>MARTHA CHARLOTE</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>VALLE</t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SALAS</t>
+          <t xml:space="preserve">MULLER </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3695,32 +3687,32 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>8441607089</t>
+          <t>8444274800</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>C IRAN 639</t>
+          <t xml:space="preserve">PLAYA EL PALMAR </t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>16-11-1992</t>
+          <t>16-06-1984</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>LUISRODRIGOVALLE@HOTMAIL.COM</t>
+          <t>CHARLOTTEPVEM@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>02-03-2026 09:58:47</t>
+          <t>02-03-2026 16:44:57</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3730,22 +3722,22 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>02-03-2026 10:03:47</t>
+          <t>02-03-2026 16:51:01</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3755,7 +3747,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>02-03-2026 10:02:56</t>
+          <t>02-03-2026 16:49:45</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3765,7 +3757,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3775,14 +3767,14 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26330522787040003084</t>
+          <t>26330522803450003142</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3799,12 +3791,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>347500</t>
+          <t>347703</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>89665</t>
+          <t>89868</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3814,17 +3806,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>GUSTAVO</t>
+          <t xml:space="preserve">MARIA JULIA </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3834,32 +3826,32 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>8441967822</t>
+          <t>8444972157</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>LONGIN 244</t>
+          <t>PLAYA PALMAR</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>21-04-1994</t>
+          <t>13-01-2002</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>GUSTAVOGUERREROHDZ21@GMAIL.COM</t>
+          <t>MARIAJULIARODGON12@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>02-03-2026 11:04:17</t>
+          <t>02-03-2026 16:46:35</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3884,7 +3876,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>02-03-2026 11:09:31</t>
+          <t>02-03-2026 16:56:06</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3894,7 +3886,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>02-03-2026 11:08:44</t>
+          <t>02-03-2026 16:55:49</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3914,7 +3906,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26330522788690003086</t>
+          <t>26330522803920003147</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
@@ -3938,12 +3930,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>347524</t>
+          <t>347741</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>89689</t>
+          <t>89906</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3953,17 +3945,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VICTOR MANUEL</t>
+          <t xml:space="preserve">VALERIA </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTOS </t>
+          <t xml:space="preserve">RAMIREZ </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3973,32 +3965,28 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>8771085725</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C MARMOL </t>
-        </is>
-      </c>
+          <t>8444556056</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>13-11-1958</t>
+          <t>05-04-2013</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>VICMANSAN1@HOTMAIL.COM</t>
+          <t>LUIS.RAMIREZ@VOSS.NET</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>02-03-2026 12:04:48</t>
+          <t>02-03-2026 17:24:53</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -4008,44 +3996,36 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>3 MESES $2,099</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>699.67</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>02-03-2026 12:13:12</t>
+          <t>02-03-2026 17:26:15</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>02-03-2026 12:12:09</t>
-        </is>
-      </c>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4053,14 +4033,14 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26330522790550003092</t>
+          <t>26330522806500003160</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -4077,12 +4057,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>347560</t>
+          <t>347470</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>89725</t>
+          <t>89635</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4092,17 +4072,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>JOANA MELISSA</t>
+          <t>ABEL FRANCISCO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEÑA </t>
+          <t>FIGUEROA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">TORRES </t>
+          <t>MONSIVAIS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4112,32 +4092,32 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>8446072138</t>
+          <t>8442771751</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>JESUS CABELLO</t>
+          <t>PLAZA DE MORELIA 148</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>22-01-2001</t>
+          <t>28-11-1997</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>MELISS12_@HOTMAIL.COM</t>
+          <t>ABEL_SW94@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>02-03-2026 13:15:33</t>
+          <t>02-03-2026 09:49:13</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -4147,22 +4127,22 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>02-03-2026 13:20:22</t>
+          <t>02-03-2026 09:56:44</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -4172,7 +4152,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>02-03-2026 13:19:38</t>
+          <t>02-03-2026 09:56:01</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4182,7 +4162,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -4192,14 +4172,14 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26330522792850003094</t>
+          <t>26330522786770003083</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -4216,12 +4196,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>347659</t>
+          <t>347476</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>89824</t>
+          <t>89641</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4231,17 +4211,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">HANNA DANIELA </t>
+          <t xml:space="preserve">LUIS RODRIGO </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMIREZ </t>
+          <t>VALLE</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARMONA </t>
+          <t>SALAS</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4251,32 +4231,32 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>8443880461</t>
+          <t>8441607089</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>NISPERO 300</t>
+          <t>C IRAN 639</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>22-12-2003</t>
+          <t>16-11-1992</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>HANNARMZ2003@GMAIL.COM</t>
+          <t>LUISRODRIGOVALLE@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>02-03-2026 16:04:35</t>
+          <t>02-03-2026 09:58:47</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4301,7 +4281,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>02-03-2026 16:07:03</t>
+          <t>02-03-2026 10:03:47</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -4311,7 +4291,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>02-03-2026 16:06:28</t>
+          <t>02-03-2026 10:02:56</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4331,7 +4311,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26330522800060003129</t>
+          <t>26330522787040003084</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
@@ -4343,24 +4323,24 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Enrique Ramos Calvillo</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>347511</t>
+          <t>347500</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>89676</t>
+          <t>89665</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4370,17 +4350,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>XIMENA</t>
+          <t>GUSTAVO</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>HUMARAN</t>
+          <t>GUERRERO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CALDERON</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4390,32 +4370,32 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>8715683348</t>
+          <t>8441967822</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">C DE LA CANTERA </t>
+          <t>LONGIN 244</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>06-11-2004</t>
+          <t>21-04-1994</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>XIMENAHUMC@GMAIL.COM</t>
+          <t>GUSTAVOGUERREROHDZ21@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>02-03-2026 11:42:38</t>
+          <t>02-03-2026 11:04:17</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4425,22 +4405,22 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>02-03-2026 11:47:59</t>
+          <t>02-03-2026 11:09:31</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -4450,7 +4430,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>02-03-2026 11:47:04</t>
+          <t>02-03-2026 11:08:44</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4470,14 +4450,14 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26330522789760003088</t>
+          <t>26330522788690003086</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -4494,12 +4474,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>347638</t>
+          <t>347524</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>89803</t>
+          <t>89689</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4509,17 +4489,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">OMAR </t>
+          <t>VICTOR MANUEL</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t xml:space="preserve">SANTOS </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUGO </t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4529,12 +4509,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>8441025582</t>
+          <t>8771085725</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>VILLA SANTA ELENA 185</t>
+          <t xml:space="preserve">C MARMOL </t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4544,17 +4524,17 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>15-12-1969</t>
+          <t>13-11-1958</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>DMTYGALO@GMAIL.COM</t>
+          <t>VICMANSAN1@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>02-03-2026 15:37:11</t>
+          <t>02-03-2026 12:04:48</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4564,22 +4544,22 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>02-03-2026 15:43:24</t>
+          <t>02-03-2026 12:13:12</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -4589,7 +4569,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>02-03-2026 15:42:29</t>
+          <t>02-03-2026 12:12:09</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4599,7 +4579,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -4609,14 +4589,14 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26330522798470003120</t>
+          <t>26330522790550003092</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -4633,12 +4613,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>347693</t>
+          <t>347560</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>89858</t>
+          <t>89725</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4648,17 +4628,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DANNA PATRICIA</t>
+          <t>JOANA MELISSA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORENO </t>
+          <t xml:space="preserve">PEÑA </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PESINA</t>
+          <t xml:space="preserve">TORRES </t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4668,12 +4648,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8444481303</t>
+          <t>8446072138</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>VILLAS DE RANCHO</t>
+          <t>JESUS CABELLO</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4683,17 +4663,17 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>11-05-1979</t>
+          <t>22-01-2001</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>DANNA.MORENO@YAHOO.COM.MX</t>
+          <t>MELISS12_@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>02-03-2026 16:41:23</t>
+          <t>02-03-2026 13:15:33</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4703,22 +4683,22 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>02-03-2026 16:45:59</t>
+          <t>02-03-2026 13:20:22</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4728,7 +4708,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>02-03-2026 16:45:24</t>
+          <t>02-03-2026 13:19:38</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4748,14 +4728,14 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26330522802950003141</t>
+          <t>26330522792850003094</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -4772,12 +4752,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>347728</t>
+          <t>347659</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>89893</t>
+          <t>89824</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4787,17 +4767,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">PABLO  </t>
+          <t xml:space="preserve">HANNA DANIELA </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">VELAZQUEZ </t>
+          <t xml:space="preserve">RAMIREZ </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLORES </t>
+          <t xml:space="preserve">CARMONA </t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4807,32 +4787,32 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>8441104535</t>
+          <t>8443880461</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZONA CENTRO </t>
+          <t>NISPERO 300</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>16-01-2001</t>
+          <t>22-12-2003</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>PABLOCHARLESSV@GMAIL.COM</t>
+          <t>HANNARMZ2003@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>02-03-2026 17:16:48</t>
+          <t>02-03-2026 16:04:35</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4857,7 +4837,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>02-03-2026 17:25:15</t>
+          <t>02-03-2026 16:07:03</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4867,7 +4847,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>02-03-2026 17:22:49</t>
+          <t>02-03-2026 16:06:28</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4877,7 +4857,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -4887,7 +4867,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26330522806360003159</t>
+          <t>26330522800060003129</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
@@ -4911,12 +4891,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>347743</t>
+          <t>348450</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>89908</t>
+          <t>90615</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4926,17 +4906,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAULA MARIA </t>
+          <t xml:space="preserve">PEDRO </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESQUIVEL </t>
+          <t xml:space="preserve">CAMPOS </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>DAVILA</t>
+          <t xml:space="preserve">MENDOZA </t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4946,32 +4926,32 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>8444642288</t>
+          <t>8446079475</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>VILLA VERGEL</t>
+          <t>SAN EZEQUIEL 111</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>05-09-2009</t>
+          <t>23-08-2000</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>PAO.ESQUIVEL0509@GMAIL.COM</t>
+          <t>PEDRO.MENDOZACAMPOS.3@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>02-03-2026 17:29:51</t>
+          <t>04-03-2026 15:01:11</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4986,27 +4966,27 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>02-03-2026 17:49:36</t>
+          <t>04-03-2026 15:04:30</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>02-03-2026 17:47:45</t>
+          <t>04-03-2026 15:03:27</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -5016,7 +4996,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -5026,18 +5006,14 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26330522808470003167</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26330522884330003312</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -5054,12 +5030,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>348045</t>
+          <t>347638</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>90210</t>
+          <t>89803</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5069,17 +5045,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDGAR ALEJANDRO </t>
+          <t xml:space="preserve">OMAR </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARLOS </t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t xml:space="preserve">LUGO </t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -5089,12 +5065,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>8444420576</t>
+          <t>8441025582</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>LOC HEDIONDA GRANDE</t>
+          <t>VILLA SANTA ELENA 185</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5104,17 +5080,17 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>25-06-1986</t>
+          <t>15-12-1969</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>EDGAR.CARLOS@LIVE.COM.MX</t>
+          <t>DMTYGALO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>03-03-2026 13:30:38</t>
+          <t>02-03-2026 15:37:11</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -5139,17 +5115,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>03-03-2026 13:39:46</t>
+          <t>02-03-2026 15:43:24</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>03-03-2026 13:37:22</t>
+          <t>02-03-2026 15:42:29</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -5169,7 +5145,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26330522840330003215</t>
+          <t>26330522798470003120</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
@@ -5193,12 +5169,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>347172</t>
+          <t>347693</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>89337</t>
+          <t>89858</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5208,17 +5184,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>DEYDA BERENICE</t>
+          <t>DANNA PATRICIA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>VITELA</t>
+          <t xml:space="preserve">MORENO </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>PESINA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5228,12 +5204,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>8448087408</t>
+          <t>8444481303</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>REAL DE PEÑA</t>
+          <t>VILLAS DE RANCHO</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5243,17 +5219,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>27-11-1978</t>
+          <t>11-05-1979</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>DEBEVICO@HOTMAIL.COM</t>
+          <t>DANNA.MORENO@YAHOO.COM.MX</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>28-02-2026 09:48:36</t>
+          <t>02-03-2026 16:41:23</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5263,32 +5239,32 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>02-03-2026 18:12:51</t>
+          <t>02-03-2026 16:45:59</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>02-03-2026 18:11:48</t>
+          <t>02-03-2026 16:45:24</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5298,7 +5274,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -5308,22 +5284,14 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26330522810710003172</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>CHRISTIAN EDGARDO MARQUEZ DE LUNA</t>
-        </is>
-      </c>
+          <t>26330522802950003141</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -5340,12 +5308,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>347276</t>
+          <t>347728</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>89441</t>
+          <t>89893</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5355,17 +5323,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">SI </t>
+          <t xml:space="preserve">PABLO  </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>PING</t>
+          <t xml:space="preserve">VELAZQUEZ </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ZENG</t>
+          <t xml:space="preserve">FLORES </t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5375,10 +5343,14 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>5577351941</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>8441104535</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZONA CENTRO </t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5386,17 +5358,17 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>26-02-1992</t>
+          <t>16-01-2001</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>MARCOS120734@GMAIL.COM</t>
+          <t>PABLOCHARLESSV@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>01-03-2026 08:47:50</t>
+          <t>02-03-2026 17:16:48</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -5406,36 +5378,44 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>3 MESES $2,099</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>699.67</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>01-03-2026 08:50:14</t>
+          <t>02-03-2026 17:25:15</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:22:49</t>
+        </is>
+      </c>
       <c r="U36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W36" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5443,14 +5423,14 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26330522765180003033</t>
+          <t>26330522806360003159</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -5467,12 +5447,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>347466</t>
+          <t>347743</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>89631</t>
+          <t>89908</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5482,17 +5462,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>MARTIN ALEJANDRO</t>
+          <t xml:space="preserve">PAULA MARIA </t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t xml:space="preserve">ESQUIVEL </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Y GAMEZ</t>
+          <t>DAVILA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5502,32 +5482,32 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>8442734289</t>
+          <t>8444642288</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>PRIV BRUCELAS</t>
+          <t>VILLA VERGEL</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>07-09-2008</t>
+          <t>05-09-2009</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>MARINNNALEJANDRO@HOTMAIL.COM</t>
+          <t>PAO.ESQUIVEL0509@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>02-03-2026 09:35:39</t>
+          <t>02-03-2026 17:29:51</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5537,22 +5517,22 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>02-03-2026 09:41:18</t>
+          <t>02-03-2026 17:49:36</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -5562,7 +5542,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>02-03-2026 09:39:57</t>
+          <t>02-03-2026 17:47:45</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -5572,7 +5552,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -5582,14 +5562,18 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26330522786190003082</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr"/>
+          <t>26330522808470003167</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -5745,12 +5729,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>347703</t>
+          <t>345411</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>89868</t>
+          <t>87576</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5760,17 +5744,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA JULIA </t>
+          <t xml:space="preserve">JOSE ARMANDO </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>PIZAÑA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5780,32 +5764,32 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>8444972157</t>
+          <t>8661612658</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>PLAYA PALMAR</t>
+          <t>COLONIA RANCHO DE PEÑA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>13-01-2002</t>
+          <t>19-09-2002</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>MARIAJULIARODGON12@GMAIL.COM</t>
+          <t>JOSEARMANDO190902@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>02-03-2026 16:46:35</t>
+          <t>20-02-2026 19:45:12</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5830,17 +5814,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>02-03-2026 16:56:06</t>
+          <t>03-03-2026 16:39:11</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>02-03-2026 16:55:49</t>
+          <t>03-03-2026 16:38:34</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5850,7 +5834,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -5860,11 +5844,19 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26330522803920003147</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
+          <t>26330522847440003233</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>SERGIO AARON CRUZ RODRIGUEZ</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>649</t>
@@ -5884,12 +5876,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>347741</t>
+          <t>348556</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>89906</t>
+          <t>90721</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5899,17 +5891,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALERIA </t>
+          <t xml:space="preserve">CRISTO ISRAEL </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMIREZ </t>
+          <t xml:space="preserve">GUERRA </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5919,28 +5911,32 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>8444556056</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>4622902468</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZONA CENTRO </t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>05-04-2013</t>
+          <t>01-06-1996</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>LUIS.RAMIREZ@VOSS.NET</t>
+          <t>KRLACRISRODRIMENDO1722@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>02-03-2026 17:24:53</t>
+          <t>04-03-2026 18:12:26</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5950,36 +5946,44 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>3 MESES $2,099</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>699.67</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>02-03-2026 17:26:15</t>
+          <t>04-03-2026 18:15:40</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr"/>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:15:02</t>
+        </is>
+      </c>
       <c r="U40" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr"/>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W40" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5987,14 +5991,14 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26330522806500003160</t>
+          <t>26330522893650003355</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -6011,12 +6015,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>347948</t>
+          <t>348768</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>90113</t>
+          <t>90933</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -6026,17 +6030,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">VELLATHUR </t>
+          <t xml:space="preserve">DANIEL </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RAMESH</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>GAYATHIRI</t>
+          <t xml:space="preserve">PONCE </t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -6046,32 +6050,32 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>8445922584</t>
+          <t>8443527698</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>CAÑADA ANCHA</t>
+          <t xml:space="preserve">PRIVA MARMOL </t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>20-05-1994</t>
+          <t>19-04-1981</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>GAYATHIRIIVINODH@GMAIL.COM</t>
+          <t>DGARCIA_04@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>03-03-2026 07:22:19</t>
+          <t>05-03-2026 17:33:29</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -6096,17 +6100,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>03-03-2026 07:54:44</t>
+          <t>05-03-2026 19:29:13</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>06-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>03-03-2026 07:53:56</t>
+          <t>05-03-2026 19:28:36</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -6126,15 +6130,19 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26330522832440003203</t>
+          <t>26330522929510003434</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>CHRISTIAN EDGARDO MARQUEZ DE LUNA</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>649</t>
@@ -6154,12 +6162,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>348266</t>
+          <t>347948</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>90431</t>
+          <t>90113</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6169,17 +6177,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>EDUARDO</t>
+          <t xml:space="preserve">VELLATHUR </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>RAMESH</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CARRILLO</t>
+          <t>GAYATHIRI</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6189,32 +6197,32 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>8446743787</t>
+          <t>8445922584</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>GUAYULERA</t>
+          <t>CAÑADA ANCHA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>25-04-2004</t>
+          <t>20-05-1994</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>RODRIGUEZCARRILLOEDORDO7@GMAIL.COM</t>
+          <t>GAYATHIRIIVINODH@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>03-03-2026 19:25:46</t>
+          <t>03-03-2026 07:22:19</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -6239,7 +6247,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>03-03-2026 19:30:40</t>
+          <t>03-03-2026 07:54:44</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -6249,7 +6257,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>03-03-2026 19:29:57</t>
+          <t>03-03-2026 07:53:56</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -6259,7 +6267,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -6269,10 +6277,14 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26330522858970003271</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr"/>
+          <t>26330522832440003203</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
@@ -6281,24 +6293,24 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexander Osorio Padua</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>348191</t>
+          <t>347946</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>90356</t>
+          <t>90111</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6308,17 +6320,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>JOSUE NERIM</t>
+          <t>SEVANNA ARUNAGIRI</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASAS </t>
+          <t>VINODH</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MOLINA</t>
+          <t>KUMAR</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6328,12 +6340,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>8443516231</t>
+          <t>8442891827</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">HACIENDA SAN RAFAEL </t>
+          <t xml:space="preserve">CAÑADA ANCHA </t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6343,17 +6355,17 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>18-02-1992</t>
+          <t>02-12-1990</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>JOSUENERIM.1802@GMAIL.COM</t>
+          <t>VINODHARUNAGIRI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>03-03-2026 17:44:52</t>
+          <t>03-03-2026 07:18:02</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -6378,7 +6390,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>03-03-2026 17:50:53</t>
+          <t>03-03-2026 07:50:25</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -6388,7 +6400,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>03-03-2026 17:50:11</t>
+          <t>03-03-2026 07:49:38</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -6398,7 +6410,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -6408,10 +6420,14 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26330522852250003253</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr"/>
+          <t>26330522832300003202</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
@@ -6426,6 +6442,3215 @@
       <c r="AC43" t="inlineStr">
         <is>
           <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>348497</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>90662</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARIANA DENISE </t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VENEGAS </t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>8443922960</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>BRISAS</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>30-09-1997</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>DNSVENEGAS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>04-03-2026 16:55:56</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>04-03-2026 17:16:38</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>04-03-2026 17:16:07</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>26330522889870003338</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>348572</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>90737</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RODRIGO </t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARTINEZ </t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TANACA </t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>8444594387</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HACIENDA EL CORTIJO </t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>04-06-2003</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>TANACARODRIGOMARTINEZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:37:04</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:40:21</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:39:35</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>26330522895080003360</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>348191</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>90356</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>JOSUE NERIM</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CASAS </t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>MOLINA</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>8443516231</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HACIENDA SAN RAFAEL </t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>18-02-1992</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>JOSUENERIM.1802@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:44:52</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:50:53</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:50:11</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>26330522852250003253</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>347395</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>89560</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FERNANDA MITCHELL </t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>OCHOA</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>RIESTRA</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>8448587771</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIA REAL </t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>18-01-2002</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>FERNANDAMITCHEL8A@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>02-03-2026 05:57:55</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>RECURRENTE $799 HE</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>02-03-2026 06:08:53</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>02-03-2026 06:07:47</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>26330522774380003069</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>348266</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>90431</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>CARRILLO</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>8446743787</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>GUAYULERA</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>25-04-2004</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>RODRIGUEZCARRILLOEDORDO7@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:25:46</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:30:40</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:29:57</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>26330522858970003271</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>348377</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>90542</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JAVIER </t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>8446747749</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>PLAYA DEL PALMAR 171</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>01-10-2008</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>JAVRODGON08@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>04-03-2026 10:11:27</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>CONVENIO DOMICILIADO $549</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>04-03-2026 10:17:47</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>04-03-2026 10:17:12</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>26330522878320003300</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>348539</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>90704</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EMIGDIA CRISTELA </t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARTINEZ </t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARINES </t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>8441315452</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EL TOREO </t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>05-08-1972</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>EMY0572@YAHOO.COM.MX</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>04-03-2026 17:49:45</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>05-03-2026 17:03:27</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>05-03-2026 17:01:00</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>26330522922750003423</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>Carlos Enrique Ramos Calvillo</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>348587</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>90752</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOSE OMAR </t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACOSTA </t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TORRES </t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>4775219661</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CALLE 2 </t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>17-01-2000</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>OMARA4999@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>04-03-2026 19:14:34</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>CONVENIO DOMICILIADO $549</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>04-03-2026 19:20:29</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>04-03-2026 19:19:35</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>26330522897120003365</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>348045</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>90210</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDGAR ALEJANDRO </t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CARLOS </t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>ESPINOZA</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>8444420576</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>LOC HEDIONDA GRANDE</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>25-06-1986</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>EDGAR.CARLOS@LIVE.COM.MX</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>03-03-2026 13:30:38</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>03-03-2026 13:39:46</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>03-03-2026 13:37:22</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>26330522840330003215</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>348754</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>90919</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOSE ANDRES </t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARENAS </t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AVILA </t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>8442320251</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>LAS BRISAS</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>20-08-2001</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>ANDYARE846372@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:44:04</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:52:29</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:51:24</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>26330522922280003421</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>348457</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>90622</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARTURO ALEJANDRO </t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DOMINGUEZ </t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEXICANO </t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>8442985882</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>REPUBLICA</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>05-11-2008</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>ARTEOM8@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>04-03-2026 15:10:58</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>CONVENIO DOMICILIADO $549</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>04-03-2026 17:59:26</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>04-03-2026 17:58:46</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>26330522892630003349</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>CHRISTIAN EDGARDO MARQUEZ DE LUNA</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>348462</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>90627</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IRVIN ORLANDO </t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOMEZ </t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TREVIÑO </t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>8443065137</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORIA LA CAPILLA 238 </t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>04-05-2009</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>IRVINGOMT@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>04-03-2026 15:31:01</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>CONVENIO DOMICILIADO $549</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>04-03-2026 15:38:45</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>04-03-2026 15:37:17</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>26330522885510003319</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>348550</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>90715</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ERNESTO </t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CANTU </t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>CHARLES</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>8120397067</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>LA SALLE</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>24-07-2000</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>ERNESTOCANTU333@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:01:08</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>RECURRENTE $799 HE</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:05:21</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:05:02</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>26330522892980003351</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>348719</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>90884</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIANA LAURA </t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RUIZ </t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUJAN </t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>9512812624</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>EL TOREO</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>11-06-2000</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>DIANA.RULU11@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>05-03-2026 15:13:03</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>05-03-2026 15:41:00</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>05-03-2026 15:39:33</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>26330522919390003409</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>347732</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>89897</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LUIS ANTONIO</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RAMIREZ</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>DIAZ</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>8443407772</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>07-05-2011</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>GIEZI12@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:19:27</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>3 MESES $2,099</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>699.67</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:21:11</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>26330522806080003158</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2099</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>348726</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>90891</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ISABEL ALI</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RODRIGUEZ </t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>CANIZALES</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>8442694337</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>PASEO DE LOS MIRLOS 307</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>24-05-2004</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>ISABELALIRDZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>05-03-2026 15:33:05</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>05-03-2026 15:42:59</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>05-03-2026 15:42:26</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>26330522919440003410</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>348781</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>90946</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DAVID GERARDO  </t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GARZA </t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>8441620966</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>DOCTORES</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>02-08-1973</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>AUTOSERVICIODAGAR@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>05-03-2026 17:55:13</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>05-03-2026 17:59:15</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>05-03-2026 17:58:30</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>26330522925660003428</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>348309</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>90474</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ANDREA KARELY</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEZA </t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>8781118843</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>C NAYARIT 627</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>18-01-2001</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>ANKAME99@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>04-03-2026 04:36:42</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>04-03-2026 04:44:10</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>04-03-2026 04:43:06</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>26330522863840003283</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>348501</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>90666</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GERARDO </t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARTINEZ </t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUENTE </t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>8442640012</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>BRISAS</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>05-08-1996</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>GEMAPU85@GAMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>04-03-2026 16:58:06</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>04-03-2026 17:12:15</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>04-03-2026 17:11:12</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>26330522889600003337</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>348546</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>90711</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARIAN LIZETH </t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RAMIREZ</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>PEÑA</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>8444550481</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JARDINEZ DE VERSALLES </t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>26-08-2000</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>MARIANRMZP@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>04-03-2026 17:57:17</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>RECURRENTE $799 HE</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:02:31</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:01:52</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>26330522892780003350</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>348337</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>90502</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>PABLO ALBERTO</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRAGA </t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>CARDENAS</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>5648534788</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>COL DEL VALLE</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>27-03-2003</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>CARDENAS_78@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>04-03-2026 07:51:45</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>04-03-2026 07:56:36</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>04-03-2026 07:55:52</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>26330522874830003292</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>348368</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>90533</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>FERNANDO IVAN</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>RAMIREZ</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>8120400400</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C JORNALEROS 131 </t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>13-04-1988</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>FERNANDO_RMZ@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>04-03-2026 09:30:51</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>04-03-2026 09:35:15</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>04-03-2026 09:34:12</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>26330522877490003297</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>348428</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>90593</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AIDA GABRIELA </t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>PORTER</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>CABRERA</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>8441222017</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>C ARCOS 388</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>15-07-1976</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>AGABYPORTER@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>04-03-2026 13:47:43</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>04-03-2026 13:54:06</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>04-03-2026 13:53:19</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>26330522882200003307</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>Alexander Osorio Padua</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>con rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SALTILLO VILLALTA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SALTILLO VILLALTA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC66"/>
+  <dimension ref="A1:AC74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>347290</t>
+          <t>334324</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>89455</t>
+          <t>18191</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VELLADURAI </t>
+          <t>PEDRO EMMANUEL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>KIRUTHIKA</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>KIRUTHIKA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,32 +613,32 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8321234660</t>
+          <t>8444958234</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>RANCHO DE PEÑA</t>
+          <t>RIO TAMANZUNCHALE 388</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>02-03-1999</t>
+          <t>13-03-2004</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>V.KIRTHI2399@GMAIL.COM</t>
+          <t>LARR2098@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>01-03-2026 10:03:45</t>
+          <t>13-01-2026 12:04:07</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -663,17 +663,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>01-03-2026 10:09:05</t>
+          <t>06-03-2026 12:42:10</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>01-03-2026 10:08:26</t>
+          <t>06-03-2026 12:41:30</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -693,10 +693,14 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26330522766350003039</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr"/>
+          <t>26330522948910003472</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
@@ -705,7 +709,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Alexander Osorio Padua</t>
+          <t>Carlos Enrique Ramos Calvillo</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -717,12 +721,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>347304</t>
+          <t>338269</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>89469</t>
+          <t>16087</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -732,17 +736,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DANIEL</t>
+          <t>GIEZI</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>GARZA</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -752,32 +756,28 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8442345269</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>FLORES TAPIA</t>
-        </is>
-      </c>
+          <t>8441063703</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>20-07-1996</t>
+          <t>12-10-1978</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>DANY_GARZA96@HOTMAIL.COM</t>
+          <t>GIEZID@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>01-03-2026 10:51:59</t>
+          <t>27-01-2026 08:06:24</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -787,44 +787,36 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>3 MESES $2,099</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>699.67</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>01-03-2026 11:00:49</t>
+          <t>02-03-2026 17:17:39</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>01-03-2026 10:59:52</t>
-        </is>
-      </c>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -832,18 +824,14 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26330522767210003045</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26330522805800003157</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -860,12 +848,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>346927</t>
+          <t>346355</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89092</t>
+          <t>88520</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -875,17 +863,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENRIQUE </t>
+          <t>EDGAR EMMANUEL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>BLANCO</t>
+          <t>DE LEON</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -895,10 +883,14 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8442183769</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>8443430619</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>VFVG</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -906,17 +898,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>31-08-1979</t>
+          <t>01-04-1983</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>EGBEG@HOTMAIL.COM</t>
+          <t>FASTVENDINGSALTILLO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>27-02-2026 12:07:18</t>
+          <t>25-02-2026 05:15:25</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -926,36 +918,44 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>ANUALIDAD + MES REGALO $6,999</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>538.38</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>04-03-2026 04:56:24</t>
+          <t>02-03-2026 11:00:15</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>04-04-2027 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>02-03-2026 10:59:39</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -963,7 +963,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26330522864020003284</t>
+          <t>26330522788500003085</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>6999</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -995,12 +995,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>340073</t>
+          <t>347312</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17891</t>
+          <t>89477</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1010,17 +1010,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ANDREA ALEJANDRA</t>
+          <t xml:space="preserve">DAGOBERTO </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CONTRERAS</t>
+          <t>GARZA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1030,32 +1030,32 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8444958964</t>
+          <t>8442440841</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>HUERTO 225</t>
+          <t xml:space="preserve">JOSE MARIA MORELOS </t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>06-12-2002</t>
+          <t>26-02-1991</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>LUISANDREA.06@OUTLOOK.COM</t>
+          <t>DAGO_GARZA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-02-2026 11:57:45</t>
+          <t>01-03-2026 11:02:16</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1080,17 +1080,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 15:14:31</t>
+          <t>01-03-2026 11:05:41</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>31-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>02-03-2026 15:13:54</t>
+          <t>01-03-2026 11:04:52</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1110,14 +1110,10 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26330522796990003109</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26330522767280003046</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1138,12 +1134,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>344818</t>
+          <t>340073</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>22635</t>
+          <t>17891</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1153,17 +1149,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>KEILA JUDITH</t>
+          <t>ANDREA ALEJANDRA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>CONTRERAS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1173,12 +1169,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8441861104</t>
+          <t>8444958964</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>COLONIA REPUBLICA</t>
+          <t>HUERTO 225</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1188,17 +1184,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>18-12-1995</t>
+          <t>06-12-2002</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>KEILA.ABC@OUTLOOK.COM</t>
+          <t>LUISANDREA.06@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>18-02-2026 13:53:58</t>
+          <t>02-02-2026 11:57:45</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1223,17 +1219,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 18:50:07</t>
+          <t>02-03-2026 15:14:31</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>02-03-2026 18:49:04</t>
+          <t>02-03-2026 15:13:54</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1243,7 +1239,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1253,12 +1249,12 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26330522814060003178</t>
+          <t>26330522796990003109</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr"/>
@@ -1281,12 +1277,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>338269</t>
+          <t>344818</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16087</t>
+          <t>22635</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1296,17 +1292,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>GIEZI</t>
+          <t>KEILA JUDITH</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1316,10 +1312,14 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8441063703</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>8441861104</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>COLONIA REPUBLICA</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1327,17 +1327,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>12-10-1978</t>
+          <t>18-12-1995</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>GIEZID@HOTMAIL.COM</t>
+          <t>KEILA.ABC@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>27-01-2026 08:06:24</t>
+          <t>18-02-2026 13:53:58</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1347,36 +1347,44 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>3 MESES $2,099</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>699.67</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 17:17:39</t>
+          <t>02-03-2026 18:50:07</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:49:04</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1384,14 +1392,18 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26330522805800003157</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
+          <t>26330522814060003178</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1408,12 +1420,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347459</t>
+          <t>346927</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89624</t>
+          <t>89092</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1423,17 +1435,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">RICARDO </t>
+          <t xml:space="preserve">ENRIQUE </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOLEDO </t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>BLANCO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1443,14 +1455,10 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8441225811</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>RIO MISSISSIPI 215</t>
-        </is>
-      </c>
+          <t>8442183769</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1458,17 +1466,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>04-08-1985</t>
+          <t>31-08-1979</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>RTV_26720@HOTMAIL.COM</t>
+          <t>EGBEG@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 08:58:04</t>
+          <t>27-02-2026 12:07:18</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1478,44 +1486,36 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>ANUALIDAD + MES REGALO $6,999</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>538.38</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 09:12:03</t>
+          <t>04-03-2026 04:56:24</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>02-03-2026 09:10:56</t>
-        </is>
-      </c>
+          <t>03-04-2027 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1523,18 +1523,22 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26330522785400003078</t>
+          <t>26330522864020003284</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>CHRISTIAN EDGARDO MARQUEZ DE LUNA</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>6999</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1551,12 +1555,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347294</t>
+          <t>347290</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89459</t>
+          <t>89455</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1566,17 +1570,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>KANNAN</t>
+          <t xml:space="preserve">VELLADURAI </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>VINODHINI</t>
+          <t>KIRUTHIKA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>VINODHINI</t>
+          <t>KIRUTHIKA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1586,12 +1590,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8446636981</t>
+          <t>8321234660</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>FLORES CAÑDA</t>
+          <t>RANCHO DE PEÑA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1601,17 +1605,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>04-09-1996</t>
+          <t>02-03-1999</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>VINODHINIKANNAN1996@GMAIL.COM</t>
+          <t>V.KIRTHI2399@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>01-03-2026 10:14:17</t>
+          <t>01-03-2026 10:03:45</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1636,17 +1640,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>01-03-2026 10:17:22</t>
+          <t>01-03-2026 10:09:05</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>31-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>01-03-2026 10:16:36</t>
+          <t>01-03-2026 10:08:26</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1666,7 +1670,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26330522766510003040</t>
+          <t>26330522766350003039</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
@@ -1690,12 +1694,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347295</t>
+          <t>345411</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89460</t>
+          <t>87576</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1705,17 +1709,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BABU</t>
+          <t xml:space="preserve">JOSE ARMANDO </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AJITH</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>KUMAR</t>
+          <t>PIZAÑA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1725,12 +1729,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8446636984</t>
+          <t>8661612658</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">RANCHO DE PEÑA </t>
+          <t>COLONIA RANCHO DE PEÑA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1740,17 +1744,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>23-04-1997</t>
+          <t>19-09-2002</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>B.AJITHSASI0223@GMAIL.COM</t>
+          <t>JOSEARMANDO190902@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>01-03-2026 10:21:27</t>
+          <t>20-02-2026 19:45:12</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1775,17 +1779,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>01-03-2026 10:25:28</t>
+          <t>03-03-2026 16:39:11</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>01-03-2026 10:24:48</t>
+          <t>03-03-2026 16:38:34</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1795,7 +1799,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1805,11 +1809,19 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26330522766600003042</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
+          <t>26330522847440003233</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>SERGIO AARON CRUZ RODRIGUEZ</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>649</t>
@@ -1817,24 +1829,24 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Alexander Osorio Padua</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>346355</t>
+          <t>347395</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>88520</t>
+          <t>89560</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1844,17 +1856,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EDGAR EMMANUEL</t>
+          <t xml:space="preserve">FERNANDA MITCHELL </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>OCHOA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>DE LEON</t>
+          <t>RIESTRA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1864,32 +1876,32 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8443430619</t>
+          <t>8448587771</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>VFVG</t>
+          <t xml:space="preserve">VIA REAL </t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>01-04-1983</t>
+          <t>18-01-2002</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>FASTVENDINGSALTILLO@GMAIL.COM</t>
+          <t>FERNANDAMITCHEL8A@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>25-02-2026 05:15:25</t>
+          <t>02-03-2026 05:57:55</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1899,32 +1911,32 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>02-03-2026 11:00:15</t>
+          <t>02-03-2026 06:08:53</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>02-03-2026 10:59:39</t>
+          <t>02-03-2026 06:07:47</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1934,7 +1946,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1944,22 +1956,14 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26330522788500003085</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>CHRISTIAN EDGARDO MARQUEZ DE LUNA</t>
-        </is>
-      </c>
+          <t>26330522774380003069</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1976,12 +1980,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347312</t>
+          <t>347294</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>89477</t>
+          <t>89459</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1991,17 +1995,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAGOBERTO </t>
+          <t>KANNAN</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>GARZA</t>
+          <t>VINODHINI</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>VINODHINI</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2011,32 +2015,32 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8442440841</t>
+          <t>8446636981</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE MARIA MORELOS </t>
+          <t>FLORES CAÑDA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>26-02-1991</t>
+          <t>04-09-1996</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>DAGO_GARZA@HOTMAIL.COM</t>
+          <t>VINODHINIKANNAN1996@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>01-03-2026 11:02:16</t>
+          <t>01-03-2026 10:14:17</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2061,17 +2065,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>01-03-2026 11:05:41</t>
+          <t>01-03-2026 10:17:22</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>31-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>01-03-2026 11:04:52</t>
+          <t>01-03-2026 10:16:36</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2081,7 +2085,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -2091,7 +2095,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26330522767280003046</t>
+          <t>26330522766510003040</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
@@ -2103,24 +2107,24 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexander Osorio Padua</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>345884</t>
+          <t>347295</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>88049</t>
+          <t>89460</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2130,17 +2134,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN CARLOS </t>
+          <t>BABU</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CENTENO</t>
+          <t>AJITH</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">MALDONADO </t>
+          <t>KUMAR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2150,12 +2154,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8116002358</t>
+          <t>8446636984</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>H11</t>
+          <t xml:space="preserve">RANCHO DE PEÑA </t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2165,17 +2169,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>15-07-1970</t>
+          <t>23-04-1997</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CENTENOJUAN@HOTMAIL.COM</t>
+          <t>B.AJITHSASI0223@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>23-02-2026 16:40:23</t>
+          <t>01-03-2026 10:21:27</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2200,17 +2204,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>02-03-2026 09:15:34</t>
+          <t>01-03-2026 10:25:28</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>31-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>02-03-2026 09:14:39</t>
+          <t>01-03-2026 10:24:48</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2230,19 +2234,11 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26330522785540003080</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>SERGIO AARON CRUZ RODRIGUEZ</t>
-        </is>
-      </c>
+          <t>26330522766600003042</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
           <t>649</t>
@@ -2250,7 +2246,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Carlos Enrique Ramos Calvillo</t>
+          <t>Alexander Osorio Padua</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2262,12 +2258,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347287</t>
+          <t>347172</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>89452</t>
+          <t>89337</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2277,17 +2273,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">KONDURAM </t>
+          <t>DEYDA BERENICE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SANKARPANDI</t>
+          <t>VITELA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SANKARPANDI</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2297,32 +2293,32 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8446638777</t>
+          <t>8448087408</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>RANCHO DE PEÑA</t>
+          <t>REAL DE PEÑA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>28-07-1993</t>
+          <t>27-11-1978</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>SANKARPANDI589@GMAIL.COM</t>
+          <t>DEBEVICO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>01-03-2026 09:50:34</t>
+          <t>28-02-2026 09:48:36</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2347,17 +2343,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>01-03-2026 10:00:47</t>
+          <t>02-03-2026 18:12:51</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>01-03-2026 09:59:47</t>
+          <t>02-03-2026 18:11:48</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2367,7 +2363,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2377,11 +2373,19 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26330522766130003038</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
+          <t>26330522810710003172</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>CHRISTIAN EDGARDO MARQUEZ DE LUNA</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>649</t>
@@ -2389,24 +2393,24 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Alexander Osorio Padua</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347511</t>
+          <t>347276</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>89676</t>
+          <t>89441</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2416,17 +2420,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>XIMENA</t>
+          <t xml:space="preserve">SI </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HUMARAN</t>
+          <t>PING</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CALDERON</t>
+          <t>ZENG</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2436,32 +2440,28 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8715683348</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C DE LA CANTERA </t>
-        </is>
-      </c>
+          <t>5577351941</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>06-11-2004</t>
+          <t>26-02-1992</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>XIMENAHUMC@GMAIL.COM</t>
+          <t>MARCOS120734@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-03-2026 11:42:38</t>
+          <t>01-03-2026 08:47:50</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2471,44 +2471,36 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>3 MESES $2,099</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>699.67</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>02-03-2026 11:47:59</t>
+          <t>01-03-2026 08:50:14</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>02-03-2026 11:47:04</t>
-        </is>
-      </c>
+          <t>31-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2516,14 +2508,14 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26330522789760003088</t>
+          <t>26330522765180003033</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2540,12 +2532,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>347172</t>
+          <t>347410</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>89337</t>
+          <t>89575</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2555,17 +2547,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DEYDA BERENICE</t>
+          <t>ANDRES</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>VITELA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>ARENAS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2575,32 +2567,32 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8448087408</t>
+          <t>8444519851</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>REAL DE PEÑA</t>
+          <t xml:space="preserve">NUEVO ATARDECER </t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>27-11-1978</t>
+          <t>02-05-2004</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>DEBEVICO@HOTMAIL.COM</t>
+          <t>AR0884520@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>28-02-2026 09:48:36</t>
+          <t>02-03-2026 06:56:57</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2625,7 +2617,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>02-03-2026 18:12:51</t>
+          <t>04-03-2026 16:26:40</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2635,7 +2627,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>02-03-2026 18:11:48</t>
+          <t>04-03-2026 16:24:22</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2645,7 +2637,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2655,19 +2647,11 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26330522810710003172</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>CHRISTIAN EDGARDO MARQUEZ DE LUNA</t>
-        </is>
-      </c>
+          <t>26330522887260003329</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
           <t>649</t>
@@ -2687,12 +2671,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>347276</t>
+          <t>347304</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>89441</t>
+          <t>89469</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2702,17 +2686,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">SI </t>
+          <t>DANIEL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PING</t>
+          <t>GARZA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ZENG</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2722,10 +2706,14 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5577351941</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>8442345269</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>FLORES TAPIA</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2733,17 +2721,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>26-02-1992</t>
+          <t>20-07-1996</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>MARCOS120734@GMAIL.COM</t>
+          <t>DANY_GARZA96@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>01-03-2026 08:47:50</t>
+          <t>01-03-2026 10:51:59</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2753,36 +2741,44 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>3 MESES $2,099</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>699.67</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>01-03-2026 08:50:14</t>
+          <t>01-03-2026 11:00:49</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr"/>
+          <t>31-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>01-03-2026 10:59:52</t>
+        </is>
+      </c>
       <c r="U17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2790,14 +2786,18 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26330522765180003033</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr"/>
+          <t>26330522767210003045</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2814,12 +2814,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>347410</t>
+          <t>347459</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>89575</t>
+          <t>89624</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2829,17 +2829,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ANDRES</t>
+          <t xml:space="preserve">RICARDO </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t xml:space="preserve">TOLEDO </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ARENAS</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8444519851</t>
+          <t>8441225811</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">NUEVO ATARDECER </t>
+          <t>RIO MISSISSIPI 215</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2864,17 +2864,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>02-05-2004</t>
+          <t>04-08-1985</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>AR0884520@GMAIL.COM</t>
+          <t>RTV_26720@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>02-03-2026 06:56:57</t>
+          <t>02-03-2026 08:58:04</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2884,32 +2884,32 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>04-03-2026 16:26:40</t>
+          <t>02-03-2026 09:12:03</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>04-03-2026 16:24:22</t>
+          <t>02-03-2026 09:10:56</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2929,14 +2929,18 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26330522887260003329</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr"/>
+          <t>26330522785400003078</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2953,12 +2957,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>347466</t>
+          <t>345884</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>89631</t>
+          <t>88049</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2968,17 +2972,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MARTIN ALEJANDRO</t>
+          <t xml:space="preserve">JUAN CARLOS </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>CENTENO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Y GAMEZ</t>
+          <t xml:space="preserve">MALDONADO </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2988,12 +2992,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8442734289</t>
+          <t>8116002358</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>PRIV BRUCELAS</t>
+          <t>H11</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -3003,17 +3007,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>07-09-2008</t>
+          <t>15-07-1970</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>MARINNNALEJANDRO@HOTMAIL.COM</t>
+          <t>CENTENOJUAN@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>02-03-2026 09:35:39</t>
+          <t>23-02-2026 16:40:23</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3038,17 +3042,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>02-03-2026 09:41:18</t>
+          <t>02-03-2026 09:15:34</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>02-03-2026 09:39:57</t>
+          <t>02-03-2026 09:14:39</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3068,11 +3072,19 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26330522786190003082</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
+          <t>26330522785540003080</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>SERGIO AARON CRUZ RODRIGUEZ</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>649</t>
@@ -3080,24 +3092,24 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Enrique Ramos Calvillo</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>347615</t>
+          <t>347287</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>89780</t>
+          <t>89452</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3107,17 +3119,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ZAHIRA</t>
+          <t xml:space="preserve">KONDURAM </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>GARZA</t>
+          <t>SANKARPANDI</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>SANKARPANDI</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3127,32 +3139,32 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8442917170</t>
+          <t>8446638777</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZOBA CENTRO </t>
+          <t>RANCHO DE PEÑA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>16-12-1992</t>
+          <t>28-07-1993</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>DANIELA162416@GMAIL.COM</t>
+          <t>SANKARPANDI589@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>02-03-2026 15:04:37</t>
+          <t>01-03-2026 09:50:34</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3177,17 +3189,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>02-03-2026 15:17:40</t>
+          <t>01-03-2026 10:00:47</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>31-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>02-03-2026 15:07:09</t>
+          <t>01-03-2026 09:59:47</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3207,7 +3219,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26330522797160003110</t>
+          <t>26330522766130003038</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
@@ -3219,24 +3231,24 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexander Osorio Padua</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>347665</t>
+          <t>347732</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>89830</t>
+          <t>89897</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3246,17 +3258,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>KARINA MONTSERRAT</t>
+          <t>LUIS ANTONIO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MEDELLIN</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3266,32 +3278,28 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>8443422445</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>EUROPA</t>
-        </is>
-      </c>
+          <t>8443407772</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>10-07-2003</t>
+          <t>07-05-2011</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>MMEDELLIN.1089@GMAIL.COM</t>
+          <t>GIEZI12@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>02-03-2026 16:10:21</t>
+          <t>02-03-2026 17:19:27</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3301,44 +3309,36 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>3 MESES $2,099</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>699.67</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>02-03-2026 16:14:32</t>
+          <t>02-03-2026 17:21:11</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>02-03-2026 16:14:00</t>
-        </is>
-      </c>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3346,36 +3346,36 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26330522800610003133</t>
+          <t>26330522806080003158</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Gerardo Emmanuel Ramirez Sanchez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>347714</t>
+          <t>347615</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>89879</t>
+          <t>89780</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3385,17 +3385,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTHA ALICIA </t>
+          <t>ZAHIRA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">RIVERA </t>
+          <t>GARZA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAUCEDO </t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3405,12 +3405,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>8442646668</t>
+          <t>8442917170</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>PORTAL</t>
+          <t xml:space="preserve">ZOBA CENTRO </t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3420,17 +3420,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>03-08-1958</t>
+          <t>16-12-1992</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>RIVALICIA111@GMAIL.COM</t>
+          <t>DANIELA162416@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>02-03-2026 16:59:22</t>
+          <t>02-03-2026 15:04:37</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3440,32 +3440,32 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>03-03-2026 16:53:07</t>
+          <t>02-03-2026 15:17:40</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>03-03-2026 16:52:11</t>
+          <t>02-03-2026 15:07:09</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3485,18 +3485,14 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26330522848380003240</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26330522797160003110</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3513,12 +3509,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>347664</t>
+          <t>347665</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>89829</t>
+          <t>89830</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3528,17 +3524,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">JAZMIN ESMERALDA </t>
+          <t>KARINA MONTSERRAT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANDOVAL </t>
+          <t>MEDELLIN</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3548,12 +3544,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>8445411918</t>
+          <t>8443422445</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>RAMOS ARIZAPE</t>
+          <t>EUROPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3563,17 +3559,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>04-09-2002</t>
+          <t>10-07-2003</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>ESMERALDASANDOVAL0409@GMAIL.COM</t>
+          <t>MMEDELLIN.1089@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>02-03-2026 16:09:58</t>
+          <t>02-03-2026 16:10:21</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3583,32 +3579,32 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>02-03-2026 16:13:39</t>
+          <t>02-03-2026 16:14:32</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>02-03-2026 16:13:01</t>
+          <t>02-03-2026 16:14:00</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3618,7 +3614,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3628,14 +3624,14 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26330522800540003132</t>
+          <t>26330522800610003133</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3652,12 +3648,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>347700</t>
+          <t>347714</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>89865</t>
+          <t>89879</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3667,17 +3663,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MARTHA CHARLOTE</t>
+          <t xml:space="preserve">MARTHA ALICIA </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t xml:space="preserve">RIVERA </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">MULLER </t>
+          <t xml:space="preserve">SAUCEDO </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3687,12 +3683,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>8444274800</t>
+          <t>8442646668</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLAYA EL PALMAR </t>
+          <t>PORTAL</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3702,17 +3698,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>16-06-1984</t>
+          <t>03-08-1958</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CHARLOTTEPVEM@GMAIL.COM</t>
+          <t>RIVALICIA111@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>02-03-2026 16:44:57</t>
+          <t>02-03-2026 16:59:22</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3722,22 +3718,22 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>02-03-2026 16:51:01</t>
+          <t>03-03-2026 16:53:07</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3747,7 +3743,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>02-03-2026 16:49:45</t>
+          <t>03-03-2026 16:52:11</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3767,14 +3763,18 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26330522803450003142</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr"/>
+          <t>26330522848380003240</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3791,12 +3791,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>347703</t>
+          <t>347466</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>89868</t>
+          <t>89631</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3806,17 +3806,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA JULIA </t>
+          <t>MARTIN ALEJANDRO</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>Y GAMEZ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3826,32 +3826,32 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>8444972157</t>
+          <t>8442734289</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>PLAYA PALMAR</t>
+          <t>PRIV BRUCELAS</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>13-01-2002</t>
+          <t>07-09-2008</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>MARIAJULIARODGON12@GMAIL.COM</t>
+          <t>MARINNNALEJANDRO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>02-03-2026 16:46:35</t>
+          <t>02-03-2026 09:35:39</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3876,17 +3876,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>02-03-2026 16:56:06</t>
+          <t>02-03-2026 09:41:18</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>02-03-2026 16:55:49</t>
+          <t>02-03-2026 09:39:57</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26330522803920003147</t>
+          <t>26330522786190003082</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
@@ -3930,12 +3930,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>347741</t>
+          <t>347651</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>89906</t>
+          <t>89816</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3945,17 +3945,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALERIA </t>
+          <t>GUILLERMO ROOSEVELTH</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMIREZ </t>
+          <t>NEIRA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3965,28 +3965,32 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>8444556056</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>8442180364</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>NORIA ARTEAGA 186</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>05-04-2013</t>
+          <t>15-07-1990</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>LUIS.RAMIREZ@VOSS.NET</t>
+          <t>ROOSEVELTH_SANTOS@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>02-03-2026 17:24:53</t>
+          <t>02-03-2026 15:51:57</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3996,36 +4000,44 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>3 MESES $2,099</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>699.67</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>02-03-2026 17:26:15</t>
+          <t>02-03-2026 15:57:46</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>02-03-2026 15:57:05</t>
+        </is>
+      </c>
       <c r="U26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W26" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4033,14 +4045,14 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26330522806500003160</t>
+          <t>26330522799370003124</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -4057,12 +4069,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>347470</t>
+          <t>347664</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>89635</t>
+          <t>89829</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4072,17 +4084,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ABEL FRANCISCO</t>
+          <t xml:space="preserve">JAZMIN ESMERALDA </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FIGUEROA</t>
+          <t xml:space="preserve">SANDOVAL </t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MONSIVAIS</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4092,32 +4104,32 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>8442771751</t>
+          <t>8445411918</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PLAZA DE MORELIA 148</t>
+          <t>RAMOS ARIZAPE</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>28-11-1997</t>
+          <t>04-09-2002</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>ABEL_SW94@HOTMAIL.COM</t>
+          <t>ESMERALDASANDOVAL0409@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>02-03-2026 09:49:13</t>
+          <t>02-03-2026 16:09:58</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -4127,32 +4139,32 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>02-03-2026 09:56:44</t>
+          <t>02-03-2026 16:13:39</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>02-03-2026 09:56:01</t>
+          <t>02-03-2026 16:13:01</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4162,7 +4174,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -4172,36 +4184,36 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26330522786770003083</t>
+          <t>26330522800540003132</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Gerardo Emmanuel Ramirez Sanchez</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>347476</t>
+          <t>347700</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>89641</t>
+          <t>89865</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4211,17 +4223,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS RODRIGO </t>
+          <t>MARTHA CHARLOTE</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>VALLE</t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SALAS</t>
+          <t xml:space="preserve">MULLER </t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4231,32 +4243,32 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>8441607089</t>
+          <t>8444274800</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>C IRAN 639</t>
+          <t xml:space="preserve">PLAYA EL PALMAR </t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>16-11-1992</t>
+          <t>16-06-1984</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>LUISRODRIGOVALLE@HOTMAIL.COM</t>
+          <t>CHARLOTTEPVEM@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>02-03-2026 09:58:47</t>
+          <t>02-03-2026 16:44:57</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4266,32 +4278,32 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>02-03-2026 10:03:47</t>
+          <t>02-03-2026 16:51:01</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>02-03-2026 10:02:56</t>
+          <t>02-03-2026 16:49:45</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4301,7 +4313,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -4311,36 +4323,36 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26330522787040003084</t>
+          <t>26330522803450003142</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Carlos Enrique Ramos Calvillo</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>347500</t>
+          <t>347703</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>89665</t>
+          <t>89868</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4350,17 +4362,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>GUSTAVO</t>
+          <t xml:space="preserve">MARIA JULIA </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4370,32 +4382,32 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>8441967822</t>
+          <t>8444972157</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>LONGIN 244</t>
+          <t>PLAYA PALMAR</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>21-04-1994</t>
+          <t>13-01-2002</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>GUSTAVOGUERREROHDZ21@GMAIL.COM</t>
+          <t>MARIAJULIARODGON12@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>02-03-2026 11:04:17</t>
+          <t>02-03-2026 16:46:35</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4420,17 +4432,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>02-03-2026 11:09:31</t>
+          <t>02-03-2026 16:56:06</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>02-03-2026 11:08:44</t>
+          <t>02-03-2026 16:55:49</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4450,7 +4462,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26330522788690003086</t>
+          <t>26330522803920003147</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
@@ -4474,12 +4486,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>347524</t>
+          <t>347741</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>89689</t>
+          <t>89906</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4489,17 +4501,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VICTOR MANUEL</t>
+          <t xml:space="preserve">VALERIA </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTOS </t>
+          <t xml:space="preserve">RAMIREZ </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4509,32 +4521,28 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>8771085725</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C MARMOL </t>
-        </is>
-      </c>
+          <t>8444556056</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>13-11-1958</t>
+          <t>05-04-2013</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>VICMANSAN1@HOTMAIL.COM</t>
+          <t>LUIS.RAMIREZ@VOSS.NET</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>02-03-2026 12:04:48</t>
+          <t>02-03-2026 17:24:53</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4544,44 +4552,36 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>3 MESES $2,099</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>699.67</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>02-03-2026 12:13:12</t>
+          <t>02-03-2026 17:26:15</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>02-03-2026 12:12:09</t>
-        </is>
-      </c>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4589,14 +4589,14 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26330522790550003092</t>
+          <t>26330522806500003160</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -4613,12 +4613,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>347560</t>
+          <t>347470</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>89725</t>
+          <t>89635</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4628,17 +4628,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>JOANA MELISSA</t>
+          <t>ABEL FRANCISCO</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEÑA </t>
+          <t>FIGUEROA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">TORRES </t>
+          <t>MONSIVAIS</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4648,32 +4648,32 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8446072138</t>
+          <t>8442771751</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>JESUS CABELLO</t>
+          <t>PLAZA DE MORELIA 148</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>22-01-2001</t>
+          <t>28-11-1997</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>MELISS12_@HOTMAIL.COM</t>
+          <t>ABEL_SW94@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>02-03-2026 13:15:33</t>
+          <t>02-03-2026 09:49:13</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4683,32 +4683,32 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>02-03-2026 13:20:22</t>
+          <t>02-03-2026 09:56:44</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>02-03-2026 13:19:38</t>
+          <t>02-03-2026 09:56:01</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4728,14 +4728,14 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26330522792850003094</t>
+          <t>26330522786770003083</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -4752,12 +4752,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>347659</t>
+          <t>347476</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>89824</t>
+          <t>89641</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4767,17 +4767,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">HANNA DANIELA </t>
+          <t xml:space="preserve">LUIS RODRIGO </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMIREZ </t>
+          <t>VALLE</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARMONA </t>
+          <t>SALAS</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4787,32 +4787,32 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>8443880461</t>
+          <t>8441607089</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>NISPERO 300</t>
+          <t>C IRAN 639</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>22-12-2003</t>
+          <t>16-11-1992</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>HANNARMZ2003@GMAIL.COM</t>
+          <t>LUISRODRIGOVALLE@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>02-03-2026 16:04:35</t>
+          <t>02-03-2026 09:58:47</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4837,17 +4837,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>02-03-2026 16:07:03</t>
+          <t>02-03-2026 10:03:47</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>02-03-2026 16:06:28</t>
+          <t>02-03-2026 10:02:56</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26330522800060003129</t>
+          <t>26330522787040003084</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
@@ -4879,24 +4879,24 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Enrique Ramos Calvillo</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>348450</t>
+          <t>347500</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>90615</t>
+          <t>89665</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4906,17 +4906,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEDRO </t>
+          <t>GUSTAVO</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMPOS </t>
+          <t>GUERRERO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">MENDOZA </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>8446079475</t>
+          <t>8441967822</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>SAN EZEQUIEL 111</t>
+          <t>LONGIN 244</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4941,17 +4941,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>23-08-2000</t>
+          <t>21-04-1994</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>PEDRO.MENDOZACAMPOS.3@GMAIL.COM</t>
+          <t>GUSTAVOGUERREROHDZ21@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>04-03-2026 15:01:11</t>
+          <t>02-03-2026 11:04:17</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4961,32 +4961,32 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>04-03-2026 15:04:30</t>
+          <t>02-03-2026 11:09:31</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>04-03-2026 15:03:27</t>
+          <t>02-03-2026 11:08:44</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -5006,14 +5006,14 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26330522884330003312</t>
+          <t>26330522788690003086</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -5030,12 +5030,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>347638</t>
+          <t>347524</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>89803</t>
+          <t>89689</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5045,17 +5045,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">OMAR </t>
+          <t>VICTOR MANUEL</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t xml:space="preserve">SANTOS </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUGO </t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>8441025582</t>
+          <t>8771085725</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>VILLA SANTA ELENA 185</t>
+          <t xml:space="preserve">C MARMOL </t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5080,17 +5080,17 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>15-12-1969</t>
+          <t>13-11-1958</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>DMTYGALO@GMAIL.COM</t>
+          <t>VICMANSAN1@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>02-03-2026 15:37:11</t>
+          <t>02-03-2026 12:04:48</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -5100,32 +5100,32 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>02-03-2026 15:43:24</t>
+          <t>02-03-2026 12:13:12</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>02-03-2026 15:42:29</t>
+          <t>02-03-2026 12:12:09</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -5145,14 +5145,14 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26330522798470003120</t>
+          <t>26330522790550003092</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -5169,12 +5169,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>347693</t>
+          <t>347560</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>89858</t>
+          <t>89725</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5184,17 +5184,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>DANNA PATRICIA</t>
+          <t>JOANA MELISSA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORENO </t>
+          <t xml:space="preserve">PEÑA </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PESINA</t>
+          <t xml:space="preserve">TORRES </t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>8444481303</t>
+          <t>8446072138</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>VILLAS DE RANCHO</t>
+          <t>JESUS CABELLO</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5219,17 +5219,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>11-05-1979</t>
+          <t>22-01-2001</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>DANNA.MORENO@YAHOO.COM.MX</t>
+          <t>MELISS12_@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>02-03-2026 16:41:23</t>
+          <t>02-03-2026 13:15:33</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5239,32 +5239,32 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>02-03-2026 16:45:59</t>
+          <t>02-03-2026 13:20:22</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>02-03-2026 16:45:24</t>
+          <t>02-03-2026 13:19:38</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5284,14 +5284,14 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26330522802950003141</t>
+          <t>26330522792850003094</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -5308,12 +5308,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>347728</t>
+          <t>347659</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>89893</t>
+          <t>89824</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5323,17 +5323,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">PABLO  </t>
+          <t xml:space="preserve">HANNA DANIELA </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">VELAZQUEZ </t>
+          <t xml:space="preserve">RAMIREZ </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLORES </t>
+          <t xml:space="preserve">CARMONA </t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5343,32 +5343,32 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>8441104535</t>
+          <t>8443880461</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZONA CENTRO </t>
+          <t>NISPERO 300</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>16-01-2001</t>
+          <t>22-12-2003</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>PABLOCHARLESSV@GMAIL.COM</t>
+          <t>HANNARMZ2003@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>02-03-2026 17:16:48</t>
+          <t>02-03-2026 16:04:35</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -5393,17 +5393,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>02-03-2026 17:25:15</t>
+          <t>02-03-2026 16:07:03</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>02-03-2026 17:22:49</t>
+          <t>02-03-2026 16:06:28</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26330522806360003159</t>
+          <t>26330522800060003129</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
@@ -5447,12 +5447,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>347743</t>
+          <t>347511</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>89908</t>
+          <t>89676</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5462,17 +5462,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAULA MARIA </t>
+          <t>XIMENA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESQUIVEL </t>
+          <t>HUMARAN</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>DAVILA</t>
+          <t>CALDERON</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>8444642288</t>
+          <t>8715683348</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>VILLA VERGEL</t>
+          <t xml:space="preserve">C DE LA CANTERA </t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5497,17 +5497,17 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>05-09-2009</t>
+          <t>06-11-2004</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>PAO.ESQUIVEL0509@GMAIL.COM</t>
+          <t>XIMENAHUMC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>02-03-2026 17:29:51</t>
+          <t>02-03-2026 11:42:38</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5522,27 +5522,27 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>02-03-2026 17:49:36</t>
+          <t>02-03-2026 11:47:59</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>02-03-2026 17:47:45</t>
+          <t>02-03-2026 11:47:04</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -5562,18 +5562,14 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26330522808470003167</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26330522789760003088</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -5590,12 +5586,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>347651</t>
+          <t>347638</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>89816</t>
+          <t>89803</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5605,17 +5601,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>GUILLERMO ROOSEVELTH</t>
+          <t xml:space="preserve">OMAR </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>NEIRA</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t xml:space="preserve">LUGO </t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5625,12 +5621,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>8442180364</t>
+          <t>8441025582</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>NORIA ARTEAGA 186</t>
+          <t>VILLA SANTA ELENA 185</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5640,17 +5636,17 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>15-07-1990</t>
+          <t>15-12-1969</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>ROOSEVELTH_SANTOS@HOTMAIL.COM</t>
+          <t>DMTYGALO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>02-03-2026 15:51:57</t>
+          <t>02-03-2026 15:37:11</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5660,32 +5656,32 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>02-03-2026 15:57:46</t>
+          <t>02-03-2026 15:43:24</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>02-03-2026 15:57:05</t>
+          <t>02-03-2026 15:42:29</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -5705,14 +5701,14 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26330522799370003124</t>
+          <t>26330522798470003120</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -5729,12 +5725,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>345411</t>
+          <t>347693</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>87576</t>
+          <t>89858</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5744,17 +5740,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE ARMANDO </t>
+          <t>DANNA PATRICIA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t xml:space="preserve">MORENO </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PIZAÑA</t>
+          <t>PESINA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5764,32 +5760,32 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>8661612658</t>
+          <t>8444481303</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>COLONIA RANCHO DE PEÑA</t>
+          <t>VILLAS DE RANCHO</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>19-09-2002</t>
+          <t>11-05-1979</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>JOSEARMANDO190902@GMAIL.COM</t>
+          <t>DANNA.MORENO@YAHOO.COM.MX</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>20-02-2026 19:45:12</t>
+          <t>02-03-2026 16:41:23</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5799,32 +5795,32 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>03-03-2026 16:39:11</t>
+          <t>02-03-2026 16:45:59</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>03-03-2026 16:38:34</t>
+          <t>02-03-2026 16:45:24</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5834,7 +5830,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -5844,22 +5840,14 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26330522847440003233</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>SERGIO AARON CRUZ RODRIGUEZ</t>
-        </is>
-      </c>
+          <t>26330522802950003141</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -5876,12 +5864,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>348556</t>
+          <t>347728</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>90721</t>
+          <t>89893</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5891,17 +5879,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRISTO ISRAEL </t>
+          <t xml:space="preserve">PABLO  </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUERRA </t>
+          <t xml:space="preserve">VELAZQUEZ </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t xml:space="preserve">FLORES </t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5911,7 +5899,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>4622902468</t>
+          <t>8441104535</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5926,17 +5914,17 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>01-06-1996</t>
+          <t>16-01-2001</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>KRLACRISRODRIMENDO1722@GMAIL.COM</t>
+          <t>PABLOCHARLESSV@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>04-03-2026 18:12:26</t>
+          <t>02-03-2026 17:16:48</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5961,17 +5949,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>04-03-2026 18:15:40</t>
+          <t>02-03-2026 17:25:15</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>04-03-2026 18:15:02</t>
+          <t>02-03-2026 17:22:49</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5991,7 +5979,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26330522893650003355</t>
+          <t>26330522806360003159</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
@@ -6015,12 +6003,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>348768</t>
+          <t>347743</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>90933</t>
+          <t>89908</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -6030,17 +6018,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIEL </t>
+          <t xml:space="preserve">PAULA MARIA </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t xml:space="preserve">ESQUIVEL </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">PONCE </t>
+          <t>DAVILA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -6050,32 +6038,32 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>8443527698</t>
+          <t>8444642288</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRIVA MARMOL </t>
+          <t>VILLA VERGEL</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>19-04-1981</t>
+          <t>05-09-2009</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>DGARCIA_04@HOTMAIL.COM</t>
+          <t>PAO.ESQUIVEL0509@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>05-03-2026 17:33:29</t>
+          <t>02-03-2026 17:29:51</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -6085,32 +6073,32 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>05-03-2026 19:29:13</t>
+          <t>02-03-2026 17:49:36</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>06-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>05-03-2026 19:28:36</t>
+          <t>02-03-2026 17:47:45</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -6130,22 +6118,18 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26330522929510003434</t>
+          <t>26330522808470003167</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>CHRISTIAN EDGARDO MARQUEZ DE LUNA</t>
-        </is>
-      </c>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
@@ -6162,12 +6146,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>347948</t>
+          <t>347946</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>90113</t>
+          <t>90111</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6177,17 +6161,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">VELLATHUR </t>
+          <t>SEVANNA ARUNAGIRI</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RAMESH</t>
+          <t>VINODH</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>GAYATHIRI</t>
+          <t>KUMAR</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6197,32 +6181,32 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>8445922584</t>
+          <t>8442891827</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>CAÑADA ANCHA</t>
+          <t xml:space="preserve">CAÑADA ANCHA </t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>20-05-1994</t>
+          <t>02-12-1990</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>GAYATHIRIIVINODH@GMAIL.COM</t>
+          <t>VINODHARUNAGIRI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>03-03-2026 07:22:19</t>
+          <t>03-03-2026 07:18:02</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -6247,17 +6231,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>03-03-2026 07:54:44</t>
+          <t>03-03-2026 07:50:25</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>03-03-2026 07:53:56</t>
+          <t>03-03-2026 07:49:38</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -6277,7 +6261,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26330522832440003203</t>
+          <t>26330522832300003202</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -6293,24 +6277,24 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>Alexander Osorio Padua</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>347946</t>
+          <t>348045</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>90111</t>
+          <t>90210</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6320,17 +6304,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SEVANNA ARUNAGIRI</t>
+          <t xml:space="preserve">EDGAR ALEJANDRO </t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>VINODH</t>
+          <t xml:space="preserve">CARLOS </t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>KUMAR</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6340,12 +6324,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>8442891827</t>
+          <t>8444420576</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAÑADA ANCHA </t>
+          <t>LOC HEDIONDA GRANDE</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6355,17 +6339,17 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>02-12-1990</t>
+          <t>25-06-1986</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>VINODHARUNAGIRI@GMAIL.COM</t>
+          <t>EDGAR.CARLOS@LIVE.COM.MX</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>03-03-2026 07:18:02</t>
+          <t>03-03-2026 13:30:38</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -6390,17 +6374,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>03-03-2026 07:50:25</t>
+          <t>03-03-2026 13:39:46</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>03-03-2026 07:49:38</t>
+          <t>03-03-2026 13:37:22</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -6420,14 +6404,10 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26330522832300003202</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26330522840330003215</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
@@ -6448,12 +6428,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>348497</t>
+          <t>347948</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>90662</t>
+          <t>90113</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6463,17 +6443,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIANA DENISE </t>
+          <t xml:space="preserve">VELLATHUR </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>RAMESH</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">VENEGAS </t>
+          <t>GAYATHIRI</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6483,12 +6463,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>8443922960</t>
+          <t>8445922584</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>BRISAS</t>
+          <t>CAÑADA ANCHA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6498,17 +6478,17 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>30-09-1997</t>
+          <t>20-05-1994</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>DNSVENEGAS@GMAIL.COM</t>
+          <t>GAYATHIRIIVINODH@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>04-03-2026 16:55:56</t>
+          <t>03-03-2026 07:22:19</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -6533,17 +6513,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>04-03-2026 17:16:38</t>
+          <t>03-03-2026 07:54:44</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>04-03-2026 17:16:07</t>
+          <t>03-03-2026 07:53:56</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -6553,7 +6533,7 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
@@ -6563,7 +6543,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26330522889870003338</t>
+          <t>26330522832440003203</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
@@ -6579,24 +6559,24 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexander Osorio Padua</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>348572</t>
+          <t>348337</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>90737</t>
+          <t>90502</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6606,17 +6586,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGO </t>
+          <t>PABLO ALBERTO</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t xml:space="preserve">PRAGA </t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">TANACA </t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6626,12 +6606,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>8444594387</t>
+          <t>5648534788</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">HACIENDA EL CORTIJO </t>
+          <t>COL DEL VALLE</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6641,17 +6621,17 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>04-06-2003</t>
+          <t>27-03-2003</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>TANACARODRIGOMARTINEZ@GMAIL.COM</t>
+          <t>CARDENAS_78@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>04-03-2026 18:37:04</t>
+          <t>04-03-2026 07:51:45</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6676,17 +6656,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>04-03-2026 18:40:21</t>
+          <t>04-03-2026 07:56:36</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>04-03-2026 18:39:35</t>
+          <t>04-03-2026 07:55:52</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -6706,7 +6686,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26330522895080003360</t>
+          <t>26330522874830003292</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
@@ -6730,12 +6710,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>348191</t>
+          <t>348368</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>90356</t>
+          <t>90533</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6745,17 +6725,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>JOSUE NERIM</t>
+          <t>FERNANDO IVAN</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASAS </t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MOLINA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6765,12 +6745,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>8443516231</t>
+          <t>8120400400</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">HACIENDA SAN RAFAEL </t>
+          <t xml:space="preserve">C JORNALEROS 131 </t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6780,17 +6760,17 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>18-02-1992</t>
+          <t>13-04-1988</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>JOSUENERIM.1802@GMAIL.COM</t>
+          <t>FERNANDO_RMZ@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>03-03-2026 17:44:52</t>
+          <t>04-03-2026 09:30:51</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6815,7 +6795,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>03-03-2026 17:50:53</t>
+          <t>04-03-2026 09:35:15</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -6825,7 +6805,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>03-03-2026 17:50:11</t>
+          <t>04-03-2026 09:34:12</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -6845,7 +6825,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26330522852250003253</t>
+          <t>26330522877490003297</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr"/>
@@ -6869,12 +6849,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>347395</t>
+          <t>348428</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>89560</t>
+          <t>90593</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6884,17 +6864,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">FERNANDA MITCHELL </t>
+          <t xml:space="preserve">AIDA GABRIELA </t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>OCHOA</t>
+          <t>PORTER</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>RIESTRA</t>
+          <t>CABRERA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6904,12 +6884,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>8448587771</t>
+          <t>8441222017</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIA REAL </t>
+          <t>C ARCOS 388</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6919,17 +6899,17 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>18-01-2002</t>
+          <t>15-07-1976</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>FERNANDAMITCHEL8A@GMAIL.COM</t>
+          <t>AGABYPORTER@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>02-03-2026 05:57:55</t>
+          <t>04-03-2026 13:47:43</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -6939,32 +6919,32 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>02-03-2026 06:08:53</t>
+          <t>04-03-2026 13:54:06</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>02-03-2026 06:07:47</t>
+          <t>04-03-2026 13:53:19</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -6984,36 +6964,36 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26330522774380003069</t>
+          <t>26330522882200003307</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexander Osorio Padua</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>348266</t>
+          <t>348720</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>90431</t>
+          <t>90885</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -7023,17 +7003,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>EDUARDO</t>
+          <t xml:space="preserve">BENIGNO </t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>BAUTISTA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CARRILLO</t>
+          <t xml:space="preserve">MARTINEZ </t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7043,12 +7023,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>8446743787</t>
+          <t>9514656878</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>GUAYULERA</t>
+          <t>ZONA CENTRO</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -7058,17 +7038,17 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>25-04-2004</t>
+          <t>08-05-1999</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>RODRIGUEZCARRILLOEDORDO7@GMAIL.COM</t>
+          <t>BAMA_BENY@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>03-03-2026 19:25:46</t>
+          <t>05-03-2026 15:16:07</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -7078,32 +7058,32 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>03-03-2026 19:30:40</t>
+          <t>07-03-2026 12:09:59</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>06-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>03-03-2026 19:29:57</t>
+          <t>07-03-2026 12:08:30</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -7113,7 +7093,7 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
@@ -7123,14 +7103,18 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26330522858970003271</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr"/>
+          <t>26330522974770003540</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
@@ -7147,12 +7131,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>348377</t>
+          <t>348309</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>90542</t>
+          <t>90474</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7162,17 +7146,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">JAVIER </t>
+          <t>ANDREA KARELY</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t xml:space="preserve">MEZA </t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7182,32 +7166,32 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>8446747749</t>
+          <t>8781118843</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>PLAYA DEL PALMAR 171</t>
+          <t>C NAYARIT 627</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>01-10-2008</t>
+          <t>18-01-2001</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>JAVRODGON08@GMAIL.COM</t>
+          <t>ANKAME99@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>04-03-2026 10:11:27</t>
+          <t>04-03-2026 04:36:42</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -7217,32 +7201,32 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>04-03-2026 10:17:47</t>
+          <t>04-03-2026 04:44:10</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>04-03-2026 10:17:12</t>
+          <t>04-03-2026 04:43:06</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -7252,7 +7236,7 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
@@ -7262,14 +7246,14 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26330522878320003300</t>
+          <t>26330522863840003283</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
@@ -7286,12 +7270,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>348539</t>
+          <t>348501</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>90704</t>
+          <t>90666</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7301,7 +7285,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMIGDIA CRISTELA </t>
+          <t xml:space="preserve">GERARDO </t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -7311,7 +7295,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARINES </t>
+          <t xml:space="preserve">PUENTE </t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7321,32 +7305,32 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>8441315452</t>
+          <t>8442640012</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">EL TOREO </t>
+          <t>BRISAS</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>05-08-1972</t>
+          <t>05-08-1996</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>EMY0572@YAHOO.COM.MX</t>
+          <t>GEMAPU85@GAMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>04-03-2026 17:49:45</t>
+          <t>04-03-2026 16:58:06</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -7371,17 +7355,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>05-03-2026 17:03:27</t>
+          <t>04-03-2026 17:12:15</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>05-03-2026 17:01:00</t>
+          <t>04-03-2026 17:11:12</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -7401,7 +7385,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26330522922750003423</t>
+          <t>26330522889600003337</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -7417,24 +7401,24 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Carlos Enrique Ramos Calvillo</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>348587</t>
+          <t>348191</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>90752</t>
+          <t>90356</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7444,17 +7428,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE OMAR </t>
+          <t>JOSUE NERIM</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACOSTA </t>
+          <t xml:space="preserve">CASAS </t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">TORRES </t>
+          <t>MOLINA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7464,12 +7448,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4775219661</t>
+          <t>8443516231</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">CALLE 2 </t>
+          <t xml:space="preserve">HACIENDA SAN RAFAEL </t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -7479,17 +7463,17 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>17-01-2000</t>
+          <t>18-02-1992</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>OMARA4999@GMAIL.COM</t>
+          <t>JOSUENERIM.1802@GMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>04-03-2026 19:14:34</t>
+          <t>03-03-2026 17:44:52</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7499,32 +7483,32 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>04-03-2026 19:20:29</t>
+          <t>03-03-2026 17:50:53</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>04-03-2026 19:19:35</t>
+          <t>03-03-2026 17:50:11</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -7534,7 +7518,7 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -7544,14 +7528,14 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26330522897120003365</t>
+          <t>26330522852250003253</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
@@ -7568,12 +7552,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>348045</t>
+          <t>348266</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>90210</t>
+          <t>90431</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7583,17 +7567,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDGAR ALEJANDRO </t>
+          <t>EDUARDO</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARLOS </t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>CARRILLO</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7603,12 +7587,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>8444420576</t>
+          <t>8446743787</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>LOC HEDIONDA GRANDE</t>
+          <t>GUAYULERA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7618,17 +7602,17 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>25-06-1986</t>
+          <t>25-04-2004</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>EDGAR.CARLOS@LIVE.COM.MX</t>
+          <t>RODRIGUEZCARRILLOEDORDO7@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>03-03-2026 13:30:38</t>
+          <t>03-03-2026 19:25:46</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7653,17 +7637,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>03-03-2026 13:39:46</t>
+          <t>03-03-2026 19:30:40</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>03-03-2026 13:37:22</t>
+          <t>03-03-2026 19:29:57</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -7673,7 +7657,7 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -7683,7 +7667,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26330522840330003215</t>
+          <t>26330522858970003271</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
@@ -7707,12 +7691,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>348754</t>
+          <t>348377</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>90919</t>
+          <t>90542</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7722,17 +7706,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE ANDRES </t>
+          <t xml:space="preserve">JAVIER </t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARENAS </t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">AVILA </t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7742,12 +7726,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>8442320251</t>
+          <t>8446747749</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>LAS BRISAS</t>
+          <t>PLAYA DEL PALMAR 171</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7757,17 +7741,17 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>20-08-2001</t>
+          <t>01-10-2008</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>ANDYARE846372@GMAIL.COM</t>
+          <t>JAVRODGON08@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>05-03-2026 16:44:04</t>
+          <t>04-03-2026 10:11:27</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -7777,32 +7761,32 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>05-03-2026 16:52:29</t>
+          <t>04-03-2026 10:17:47</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>05-03-2026 16:51:24</t>
+          <t>04-03-2026 10:17:12</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -7812,7 +7796,7 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -7822,14 +7806,14 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26330522922280003421</t>
+          <t>26330522878320003300</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
@@ -7846,12 +7830,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>348457</t>
+          <t>348539</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>90622</t>
+          <t>90704</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7861,17 +7845,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARTURO ALEJANDRO </t>
+          <t xml:space="preserve">EMIGDIA CRISTELA </t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOMINGUEZ </t>
+          <t xml:space="preserve">MARTINEZ </t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEXICANO </t>
+          <t xml:space="preserve">MARINES </t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7881,32 +7865,32 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>8442985882</t>
+          <t>8441315452</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>REPUBLICA</t>
+          <t xml:space="preserve">EL TOREO </t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>05-11-2008</t>
+          <t>05-08-1972</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>ARTEOM8@GMAIL.COM</t>
+          <t>EMY0572@YAHOO.COM.MX</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>04-03-2026 15:10:58</t>
+          <t>04-03-2026 17:49:45</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -7916,32 +7900,32 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>04-03-2026 17:59:26</t>
+          <t>05-03-2026 17:03:27</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>04-03-2026 17:58:46</t>
+          <t>05-03-2026 17:01:00</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -7951,7 +7935,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -7961,44 +7945,40 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26330522892630003349</t>
+          <t>26330522922750003423</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>CHRISTIAN EDGARDO MARQUEZ DE LUNA</t>
-        </is>
-      </c>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Enrique Ramos Calvillo</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>348462</t>
+          <t>348497</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>90627</t>
+          <t>90662</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -8008,17 +7988,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRVIN ORLANDO </t>
+          <t xml:space="preserve">MARIANA DENISE </t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">GOMEZ </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">TREVIÑO </t>
+          <t xml:space="preserve">VENEGAS </t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -8028,32 +8008,32 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>8443065137</t>
+          <t>8443922960</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">NORIA LA CAPILLA 238 </t>
+          <t>BRISAS</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>04-05-2009</t>
+          <t>30-09-1997</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>IRVINGOMT@GMAIL.COM</t>
+          <t>DNSVENEGAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>04-03-2026 15:31:01</t>
+          <t>04-03-2026 16:55:56</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -8063,32 +8043,32 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>04-03-2026 15:38:45</t>
+          <t>04-03-2026 17:16:38</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>04-03-2026 15:37:17</t>
+          <t>04-03-2026 17:16:07</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -8108,14 +8088,18 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26330522885510003319</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr"/>
+          <t>26330522889870003338</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
@@ -8132,12 +8116,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>348550</t>
+          <t>348457</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>90715</t>
+          <t>90622</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -8147,17 +8131,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">ERNESTO </t>
+          <t xml:space="preserve">ARTURO ALEJANDRO </t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">CANTU </t>
+          <t xml:space="preserve">DOMINGUEZ </t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CHARLES</t>
+          <t xml:space="preserve">MEXICANO </t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -8167,12 +8151,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>8120397067</t>
+          <t>8442985882</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>LA SALLE</t>
+          <t>REPUBLICA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -8182,17 +8166,17 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>24-07-2000</t>
+          <t>05-11-2008</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>ERNESTOCANTU333@GMAIL.COM</t>
+          <t>ARTEOM8@GMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>04-03-2026 18:01:08</t>
+          <t>04-03-2026 15:10:58</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -8207,17 +8191,17 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>04-03-2026 18:05:21</t>
+          <t>04-03-2026 17:59:26</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -8227,7 +8211,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>04-03-2026 18:05:02</t>
+          <t>04-03-2026 17:58:46</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -8247,14 +8231,22 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26330522892980003351</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr"/>
+          <t>26330522892630003349</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>CHRISTIAN EDGARDO MARQUEZ DE LUNA</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
@@ -8271,12 +8263,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>348719</t>
+          <t>348462</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>90884</t>
+          <t>90627</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8286,17 +8278,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIANA LAURA </t>
+          <t xml:space="preserve">IRVIN ORLANDO </t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">RUIZ </t>
+          <t xml:space="preserve">GOMEZ </t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUJAN </t>
+          <t xml:space="preserve">TREVIÑO </t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8306,32 +8298,32 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>9512812624</t>
+          <t>8443065137</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>EL TOREO</t>
+          <t xml:space="preserve">NORIA LA CAPILLA 238 </t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>11-06-2000</t>
+          <t>04-05-2009</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>DIANA.RULU11@GMAIL.COM</t>
+          <t>IRVINGOMT@GMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>05-03-2026 15:13:03</t>
+          <t>04-03-2026 15:31:01</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -8341,32 +8333,32 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>05-03-2026 15:41:00</t>
+          <t>04-03-2026 15:38:45</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>05-03-2026 15:39:33</t>
+          <t>04-03-2026 15:37:17</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -8386,18 +8378,14 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26330522919390003409</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26330522885510003319</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
@@ -8414,12 +8402,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>347732</t>
+          <t>348550</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>89897</t>
+          <t>90715</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8429,17 +8417,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LUIS ANTONIO</t>
+          <t xml:space="preserve">ERNESTO </t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t xml:space="preserve">CANTU </t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>CHARLES</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8449,10 +8437,14 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>8443407772</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>8120397067</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>LA SALLE</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -8460,17 +8452,17 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>07-05-2011</t>
+          <t>24-07-2000</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>GIEZI12@GMAIL.COM</t>
+          <t>ERNESTOCANTU333@GMAIL.COM</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>02-03-2026 17:19:27</t>
+          <t>04-03-2026 18:01:08</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -8480,36 +8472,44 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>3 MESES $2,099</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>699.67</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>02-03-2026 17:21:11</t>
+          <t>04-03-2026 18:05:21</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:05:02</t>
+        </is>
+      </c>
       <c r="U58" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr"/>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W58" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8517,14 +8517,14 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>26330522806080003158</t>
+          <t>26330522892980003351</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
@@ -8541,12 +8541,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>348726</t>
+          <t>348885</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>90891</t>
+          <t>91050</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8556,17 +8556,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ISABEL ALI</t>
+          <t xml:space="preserve">PABLO </t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t xml:space="preserve">LEAL </t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CANIZALES</t>
+          <t xml:space="preserve">CAMPOS </t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8576,32 +8576,32 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>8442694337</t>
+          <t>8441764086</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>PASEO DE LOS MIRLOS 307</t>
+          <t xml:space="preserve">VALLE SAN AGUSTIN </t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>24-05-2004</t>
+          <t>11-08-1998</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>ISABELALIRDZ@GMAIL.COM</t>
+          <t>PABLO56_5@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>05-03-2026 15:33:05</t>
+          <t>06-03-2026 12:11:52</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -8611,22 +8611,22 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>05-03-2026 15:42:59</t>
+          <t>06-03-2026 12:39:15</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>05-03-2026 15:42:26</t>
+          <t>06-03-2026 12:38:30</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
@@ -8656,14 +8656,18 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>26330522919440003410</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr"/>
+          <t>26330522948860003471</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
@@ -8680,12 +8684,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>348781</t>
+          <t>348719</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>90946</t>
+          <t>90884</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8695,17 +8699,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAVID GERARDO  </t>
+          <t xml:space="preserve">DIANA LAURA </t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARZA </t>
+          <t xml:space="preserve">RUIZ </t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t xml:space="preserve">LUJAN </t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8715,32 +8719,32 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>8441620966</t>
+          <t>9512812624</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>DOCTORES</t>
+          <t>EL TOREO</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>02-08-1973</t>
+          <t>11-06-2000</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>AUTOSERVICIODAGAR@HOTMAIL.COM</t>
+          <t>DIANA.RULU11@GMAIL.COM</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>05-03-2026 17:55:13</t>
+          <t>05-03-2026 15:13:03</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -8765,17 +8769,17 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>05-03-2026 17:59:15</t>
+          <t>05-03-2026 15:41:00</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>05-03-2026 17:58:30</t>
+          <t>05-03-2026 15:39:33</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -8795,10 +8799,14 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>26330522925660003428</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr"/>
+          <t>26330522919390003409</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="inlineStr">
         <is>
@@ -8819,12 +8827,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>348309</t>
+          <t>348726</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>90474</t>
+          <t>90891</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8834,17 +8842,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ANDREA KARELY</t>
+          <t>ISABEL ALI</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEZA </t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>CANIZALES</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8854,12 +8862,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>8781118843</t>
+          <t>8442694337</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>C NAYARIT 627</t>
+          <t>PASEO DE LOS MIRLOS 307</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -8869,17 +8877,17 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>18-01-2001</t>
+          <t>24-05-2004</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>ANKAME99@HOTMAIL.COM</t>
+          <t>ISABELALIRDZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>04-03-2026 04:36:42</t>
+          <t>05-03-2026 15:33:05</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -8904,7 +8912,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>04-03-2026 04:44:10</t>
+          <t>05-03-2026 15:42:59</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -8914,7 +8922,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>04-03-2026 04:43:06</t>
+          <t>05-03-2026 15:42:26</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -8924,7 +8932,7 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
@@ -8934,7 +8942,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>26330522863840003283</t>
+          <t>26330522919440003410</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr"/>
@@ -8958,12 +8966,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>348501</t>
+          <t>348781</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>90666</t>
+          <t>90946</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8973,17 +8981,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">GERARDO </t>
+          <t xml:space="preserve">DAVID GERARDO  </t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t xml:space="preserve">GARZA </t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">PUENTE </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8993,12 +9001,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>8442640012</t>
+          <t>8441620966</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>BRISAS</t>
+          <t>DOCTORES</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -9008,17 +9016,17 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>05-08-1996</t>
+          <t>02-08-1973</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>GEMAPU85@GAMAIL.COM</t>
+          <t>AUTOSERVICIODAGAR@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>04-03-2026 16:58:06</t>
+          <t>05-03-2026 17:55:13</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -9043,7 +9051,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>04-03-2026 17:12:15</t>
+          <t>05-03-2026 17:59:15</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -9053,7 +9061,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>04-03-2026 17:11:12</t>
+          <t>05-03-2026 17:58:30</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -9073,14 +9081,10 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>26330522889600003337</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26330522925660003428</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr">
         <is>
@@ -9101,12 +9105,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>348546</t>
+          <t>348942</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>90711</t>
+          <t>91107</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -9116,17 +9120,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIAN LIZETH </t>
+          <t xml:space="preserve">GRISELDA </t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>LULE</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>PEÑA</t>
+          <t>GUEVARA</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -9136,12 +9140,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>8444550481</t>
+          <t>8448691323</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">JARDINEZ DE VERSALLES </t>
+          <t>JOSE RODRIGUEZ GONZALEZ 730</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -9151,17 +9155,17 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>26-08-2000</t>
+          <t>25-12-1967</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>MARIANRMZP@GMAIL.COM</t>
+          <t>GRISLULE@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>04-03-2026 17:57:17</t>
+          <t>06-03-2026 15:35:57</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -9171,32 +9175,32 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>04-03-2026 18:02:31</t>
+          <t>06-03-2026 15:48:03</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>04-03-2026 18:01:52</t>
+          <t>06-03-2026 15:47:03</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -9206,7 +9210,7 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
@@ -9216,14 +9220,18 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>26330522892780003350</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr"/>
+          <t>26330522953050003488</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
@@ -9240,12 +9248,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>348337</t>
+          <t>348546</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>90502</t>
+          <t>90711</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -9255,17 +9263,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>PABLO ALBERTO</t>
+          <t xml:space="preserve">MARIAN LIZETH </t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRAGA </t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>PEÑA</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -9275,32 +9283,32 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>5648534788</t>
+          <t>8444550481</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>COL DEL VALLE</t>
+          <t xml:space="preserve">JARDINEZ DE VERSALLES </t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>27-03-2003</t>
+          <t>26-08-2000</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>CARDENAS_78@HOTMAIL.COM</t>
+          <t>MARIANRMZP@GMAIL.COM</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>04-03-2026 07:51:45</t>
+          <t>04-03-2026 17:57:17</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -9310,32 +9318,32 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>04-03-2026 07:56:36</t>
+          <t>04-03-2026 18:02:31</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>04-03-2026 07:55:52</t>
+          <t>04-03-2026 18:01:52</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -9355,14 +9363,14 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>26330522874830003292</t>
+          <t>26330522892780003350</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
@@ -9379,12 +9387,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>348368</t>
+          <t>348834</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>90533</t>
+          <t>90999</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9394,17 +9402,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>FERNANDO IVAN</t>
+          <t>PAULINA LIZETH</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>BERNAL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>ALVARADO</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -9414,32 +9422,32 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>8120400400</t>
+          <t>8442799238</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">C JORNALEROS 131 </t>
+          <t>C LA NOGALERA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>13-04-1988</t>
+          <t>22-08-2006</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>FERNANDO_RMZ@HOTMAIL.COM</t>
+          <t>PAUSIB4@GMAIL.COM</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>04-03-2026 09:30:51</t>
+          <t>06-03-2026 06:21:34</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -9464,17 +9472,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>04-03-2026 09:35:15</t>
+          <t>06-03-2026 06:27:04</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>04-03-2026 09:34:12</t>
+          <t>06-03-2026 06:26:06</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -9494,7 +9502,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>26330522877490003297</t>
+          <t>26330522942130003446</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr"/>
@@ -9518,12 +9526,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>348428</t>
+          <t>348587</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>90593</t>
+          <t>90752</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9533,17 +9541,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">AIDA GABRIELA </t>
+          <t xml:space="preserve">JOSE OMAR </t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>PORTER</t>
+          <t xml:space="preserve">ACOSTA </t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CABRERA</t>
+          <t xml:space="preserve">TORRES </t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -9553,32 +9561,32 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>8441222017</t>
+          <t>4775219661</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>C ARCOS 388</t>
+          <t xml:space="preserve">CALLE 2 </t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>15-07-1976</t>
+          <t>17-01-2000</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>AGABYPORTER@GMAIL.COM</t>
+          <t>OMARA4999@GMAIL.COM</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>04-03-2026 13:47:43</t>
+          <t>04-03-2026 19:14:34</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -9588,32 +9596,32 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>04-03-2026 13:54:06</t>
+          <t>04-03-2026 19:20:29</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>04-03-2026 13:53:19</t>
+          <t>04-03-2026 19:19:35</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -9623,7 +9631,7 @@
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
@@ -9633,24 +9641,1152 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>26330522882200003307</t>
+          <t>26330522897120003365</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="inlineStr"/>
       <c r="AA66" t="inlineStr">
         <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>348754</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>90919</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOSE ANDRES </t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARENAS </t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AVILA </t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>8442320251</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>LAS BRISAS</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>20-08-2001</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>ANDYARE846372@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:44:04</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
           <t>649</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:52:29</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:51:24</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>26330522922280003421</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>348572</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>90737</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RODRIGO </t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARTINEZ </t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TANACA </t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>8444594387</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HACIENDA EL CORTIJO </t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>04-06-2003</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>TANACARODRIGOMARTINEZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:37:04</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:40:21</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:39:35</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>26330522895080003360</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>348450</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>90615</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PEDRO </t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CAMPOS </t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MENDOZA </t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>8446079475</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>SAN EZEQUIEL 111</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>23-08-2000</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>PEDRO.MENDOZACAMPOS.3@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>04-03-2026 15:01:11</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>RECURRENTE $799 HE</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>04-03-2026 15:04:30</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>04-03-2026 15:03:27</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>26330522884330003312</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>348556</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>90721</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CRISTO ISRAEL </t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GUERRA </t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>MENDOZA</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>4622902468</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZONA CENTRO </t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>01-06-1996</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>KRLACRISRODRIMENDO1722@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:12:26</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>RECURRENTE $799 HE</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:15:40</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:15:02</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>26330522893650003355</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>348723</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>90888</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUSANA </t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>LUJAN</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRAVO </t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>8448705737</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>ZONA CENTRO</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>21-01-1970</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>ZUSANALUJAN80@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>05-03-2026 15:18:51</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>07-03-2026 12:01:58</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>06-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>07-03-2026 12:00:50</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>26330522974650003538</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>348768</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>90933</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DANIEL </t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GARCIA </t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PONCE </t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>8443527698</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRIVA MARMOL </t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>19-04-1981</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>DGARCIA_04@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>05-03-2026 17:33:29</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>05-03-2026 19:29:13</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>05-03-2026 19:28:36</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>26330522929510003434</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>CHRISTIAN EDGARDO MARQUEZ DE LUNA</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
         <is>
           <t>Alexander Osorio Padua</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
+      <c r="AC72" t="inlineStr">
         <is>
           <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>348886</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>91051</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGUSTIN </t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LEAL </t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CAMPOS </t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>8441016764</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>PANAMA 170</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>30-11-1994</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>AGUSTINQCPROGRAM@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>06-03-2026 12:15:30</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>RECURRENTE $799 HE</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>06-03-2026 12:44:34</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>06-03-2026 12:43:51</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>26330522948960003473</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>348937</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>91102</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ERNESTO JAVIER </t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARIZPE </t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FUENTES </t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>8115888843</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>CALLE C JUAN CARLOS 1 155</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>27-07-1998</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>NETO159@HOTMIL.COM</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>06-03-2026 15:26:12</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>06-03-2026 15:32:20</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>06-03-2026 15:31:41</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>26330522952720003486</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr"/>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
